--- a/output/OR202603121104075460_evidence.xlsx
+++ b/output/OR202603121104075460_evidence.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-12 16:39</t>
+          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 16:46</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -655,25 +655,23 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Topical Anesthetic Gel Strawberry 1oz.</t>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Davis Dental Supply</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -681,38 +679,22 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product type</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -729,64 +711,46 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
+          <t>ProJel-20, Cherry Flavor, 60 gm Jar. 20% Benzocaine ...</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>iSmile Dental Products</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
+          <t>https://www.net32.com/ec/projel20-cherry-flavor-60-gm-jar-20-d-101965</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G5" s="9" t="n"/>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>Minimum quantity of 6 for volume discount</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr"/>
+      <c r="N5" s="9" t="inlineStr"/>
+      <c r="O5" s="9" t="inlineStr"/>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name, but same product family</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -803,64 +767,46 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
+          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>zoro.com</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
+          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>11.59</v>
+      </c>
+      <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name, but same product family</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -877,28 +823,28 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel</t>
+          <t>House Brand Strawberry flavored Topical Anesthetic Gel ...</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
+          <t>https://www.net32.com/ec/house-brand-strawberry-flavored-topical-anesthetic-gel-d-78066</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>6.5</v>
+        <v>8.68</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>1/each</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -907,14 +853,14 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -934,7 +880,7 @@
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>Same brand, but different variant</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -951,49 +897,49 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
+          <t>House Brand Strawberry Flavored Topical Anesthetic Gel ( ...</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>zoro.com</t>
+          <t>SurgiMac Dental Supply</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
+          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>11.59</v>
+        <v>3.99</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free Shipping on $100+ Orders</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1008,7 +954,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Same brand, product name, size, and variant</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1025,28 +971,28 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Opahl Topical Anesthetic Gel 20% Benzocaine</t>
+          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>iSmile Dental Products</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/opahl-topical-anesthetic-gel-20-benzocaine-raspberry-d-131159</t>
+          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>2.97</v>
+        <v>4.99</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>No minimum order required</t>
+          <t>6 for $4.49 each (10% discount)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1082,7 +1028,7 @@
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>Different brand, product name, and variant</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1099,40 +1045,40 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Gingicaine Strawberry flavored topical anesthetic ...</t>
+          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/gingicaine-strawberry-flavored-topical-anesthetic-benzocaine-20-d-20534</t>
+          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8.779999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Quantity discounts available</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -1156,7 +1102,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name, but same product family</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1173,21 +1119,23 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Product Details and Ordering - Henry Schein International</t>
+          <t>Benzo-Jel Topical Anesthetic Gel Strawberry 1oz/Jr</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Henry Schein</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>https://www.henryscheindental.com/us-en/shopping/products.aspx?productid=5700366%2C5700362%2C5700361%2C5700344%2C5700363%2C5700365%2C5700360&amp;PromoCode=TEM&amp;cdivid=international_d</t>
+          <t>https://www.supplyclinic.com/items/benzo-jel-topical-anesthetic-gel-strawberry-1oz-jr-henry-schein-inc-03-32019</t>
         </is>
       </c>
       <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -1210,7 +1158,7 @@
       <c r="O11" s="9" t="inlineStr"/>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>price None failed sanity vs Schein unit 6.29</t>
         </is>
       </c>
     </row>
@@ -1227,46 +1175,64 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel Strawberry 1oz/Jr</t>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/benzo-jel-topical-anesthetic-gel-strawberry-1oz-jr-henry-schein-inc-03-32019</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n"/>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1/each</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 6.29</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
@@ -1283,17 +1249,17 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel</t>
+          <t>GEL 1 OZ. BTL STRAWBERRY | PRO-LINE # 018-024</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
         </is>
       </c>
       <c r="F13" s="9" t="n"/>
@@ -1337,64 +1303,46 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
+          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>48</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G14" s="5" t="n"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>No minimum order condition specified</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Different brand, name, and size/form</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -1411,21 +1359,21 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>HP Mixing Tips, 4.2 mm, Yellow, 48/Pk, 100623</t>
+          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524?promo=YmFubmVyX2FkczoxMDYw</t>
+          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>13.28</v>
+        <v>23.86</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>48</v>
@@ -1437,23 +1385,23 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
@@ -1468,7 +1416,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1485,21 +1433,21 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
+          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>23.46</v>
+        <v>5.95</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>48</v>
@@ -1511,14 +1459,14 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
@@ -1527,12 +1475,12 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1542,7 +1490,7 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>Different product variant and size</t>
         </is>
       </c>
     </row>
@@ -1559,40 +1507,40 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
+          <t>Practicon HP Universal Mixing Tips, Yellow 4.2mm, Pack of 48</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>jobs.pfefferwerk.de</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
+          <t>https://jobs.pfefferwerk.de/products/practicon-hp-universal-mixing-tips-yellow-42mm-pack-of-48</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>23.86</v>
+        <v>20.8</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>48</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>1 @ $23.86, 2 @ $22.62, 5 @ $22.48</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
@@ -1601,7 +1549,7 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
@@ -1616,7 +1564,7 @@
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>Different brand and name</t>
+          <t>Different brand, but similar product name and variant</t>
         </is>
       </c>
     </row>
@@ -1633,21 +1581,21 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Mixing Tips HP Yellow 4.2mm 48/Bag</t>
+          <t>Maxima HP High Performance Mixing</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/15798/dental-city-mixing-tips-hp-yellow-42mm-48bag</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>40.13</v>
+        <v>39.73</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>48</v>
@@ -1663,14 +1611,14 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -1690,7 +1638,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>Same brand and product name, but variant description is incomplete</t>
         </is>
       </c>
     </row>
@@ -1707,33 +1655,33 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>MARK3 HIGH PERFORMANCE MIXING TIPS</t>
+          <t>Mixing Tips HP Yellow 4.2mm 48/Bag</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+          <t>https://www.dentalcity.com/product/15798/dental-city-mixing-tips-hp-yellow-42mm-48bag</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>19.12</v>
+        <v>40.13</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Larger pack</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
@@ -1749,7 +1697,7 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
@@ -1759,12 +1707,12 @@
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>Different pack quantity</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1781,24 +1729,28 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Maxima HP High Performance Mixing</t>
+          <t>HP Mixing Tips, 4.2 mm, Yellow, 48/Pk, 100623</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
+          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>64</v>
+      </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack size</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1807,18 +1759,34 @@
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr"/>
-      <c r="O20" s="5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different product name and pack quantity, scraped product name does not match title</t>
         </is>
       </c>
     </row>
@@ -1835,37 +1803,37 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>MARK3 T-Style Short HP Mixing Tips Yellow 4.2mm 48/pk.</t>
+          <t>MARK3 HIGH PERFORMANCE MIXING TIPS</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Chase Dental Supply</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>https://chasedentalsupply.com/mark3-t-style-short-hp-mixing-tips-yellow-4-2mm-48-pk/</t>
+          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>39.83</v>
+        <v>19.12</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>80</v>
@@ -1877,7 +1845,7 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1887,12 +1855,12 @@
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>Different brand, product name, and pack quantity</t>
         </is>
       </c>
     </row>
@@ -1909,245 +1877,189 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Pro-Health Healthy Gums Floss, 160M</t>
+          <t>— no public candidates found —</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/oralb-glide-prohealth-healthy-gums-floss-160m-d-184088</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>smaller pack</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Different product name, same brand and size</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>up&amp;up™ 2 count 160 count Each Floss Picks Mint</t>
+          <t>— no public candidates found —</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>https://www.target.com/p/up-up-2-count-160-count-each-floss-picks-mint/-/A-94981365</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Save $0.48 (5% off) when purchased as a bundle.</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N23" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr"/>
+      <c r="M23" s="9" t="inlineStr"/>
+      <c r="N23" s="9" t="inlineStr"/>
+      <c r="O23" s="9" t="inlineStr"/>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss Refill 160m 2/Bx ...</t>
+          <t>Prophy Angles</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+          <t>https://www.practicon.com/exam-hygiene/prophylaxis/prophy-angles/</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>236.99</v>
+      </c>
+      <c r="G24" s="5" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Same product name, brand, size and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss 160M Refill Unflavored ...</t>
+          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
+          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="G25" s="9" t="n"/>
+        <v>355.09</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>500</v>
+      </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2159,68 +2071,84 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr"/>
-      <c r="N25" s="9" t="inlineStr"/>
-      <c r="O25" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different brand and variant</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums In-Office Floss Refill, ...</t>
+          <t>ACCLEAN by Henry Schein | Prophy Angles</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>The Dental Market U.S.</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>https://thedentalmarket.net/preventives/oral-b-glide-healthy-gums-in-office-floss-refill-unflavored-160-m-2-box/</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>13.95</v>
+        <v>71.86</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
@@ -2229,7 +2157,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -2239,71 +2167,71 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Same product name, brand, size and pack quantity</t>
+          <t>Different product name and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Oral-B® Glide Healthy Gums Floss with Dispenser 160m</t>
+          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/glide-pro-health-original-floss-160m-with-dispenser/p/71016231</t>
+          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>12.59</v>
+        <v>263.85</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>smaller pack</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
@@ -2313,50 +2241,50 @@
       </c>
       <c r="O27" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>Same product name and size, different pack quantity</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Unwaxed Teflon Floss 160 ...</t>
+          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Dental Wholesale Direct</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>https://dentalwholesaledirect.com/preventives/oral-b-glide-healthy-gums-unwaxed-teflon-floss-160-meters-ea/</t>
+          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>11.95</v>
+        <v>153.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>smaller pack</t>
+          <t>Quantity discounts available</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2365,14 +2293,14 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
@@ -2387,45 +2315,45 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Same product name and size, different pack quantity</t>
+          <t>Different brand, but same product family</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss Refill w/ Disposable Vial ...</t>
+          <t>Acclean Disposable Prophy Angles Review | score: 4</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Spark Dental Co</t>
+          <t>Dental Product Shopper</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>https://sparkdentalco.com/products/oral-b-glide-healthy-gums-floss-refills-160m-with-disposable-vial-unflavored</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="G29" s="9" t="n"/>
+          <t>https://www.dentalproductshopper.com/hygiene-preventive/prophy-angles/acclean-disposable-prophy-angles/evaluation</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2433,68 +2361,54 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr"/>
+      <c r="N29" s="9" t="inlineStr"/>
+      <c r="O29" s="9" t="inlineStr"/>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>Insufficient information</t>
+          <t>price None failed sanity vs Schein unit 222.77</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss 160m Disp Vial 1/Bx ...</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>D C Dental Supply</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n"/>
+          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>69.48999999999999</v>
+      </c>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -2503,7 +2417,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
@@ -2518,116 +2432,96 @@
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Dental Floss [Individual &amp; Bulk]</t>
+          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>The Dental Market U.S.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/dental-floss-preventives-l-515-622</t>
+          <t>https://thedentalmarket.net/featured-items/luxatemp-automix-plus-fine-mixing-tips-box-of-25/</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>80.95</v>
+      </c>
+      <c r="G31" s="9" t="n"/>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>1-pack price (ordered pack: 2)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O31" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr"/>
+      <c r="N31" s="9" t="inlineStr"/>
+      <c r="O31" s="9" t="inlineStr"/>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>Different product name, brand, size and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Clear 2.1% Sodium Fluoride Treatment, 0.5</t>
+          <t>Luxatemp Plus</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182709</t>
+          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>267.97</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>449.95</v>
+      </c>
+      <c r="G32" s="5" t="n"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -2635,71 +2529,57 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Watermelon flavor) and scraped product name includes flavor</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Clinpro™ In Office 2.1% NaF Clear Fluoride Treatment</t>
+          <t>Impression Mixing Tips</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Top Quality Manufacturing, LLC</t>
+          <t>UC Dental Products</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
+          <t>http://www.ucdpi.com/impression-materials/mixing-tips.htm</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>142.49</v>
-      </c>
-      <c r="G33" s="9" t="n"/>
+        <v>11.95</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2711,65 +2591,81 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
-      <c r="N33" s="9" t="inlineStr"/>
-      <c r="O33" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different product name and brand</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>3M - Clinpro Clear Fluoride Varnish 100/Pack</t>
+          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/21837/3m-clinpro-clear-fluoride-varnish-100pack</t>
+          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>294.99</v>
+        <v>64.89</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Buy 4, Get 1 Free</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>95</v>
@@ -2781,7 +2677,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -2796,57 +2692,57 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Mint flavor)</t>
+          <t>Marketing-name variation of the same product line</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Treatment</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/3m-clinpro-clear-fluoride-treatment.html</t>
+          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>133.95</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Smaller pack size (50)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -2865,62 +2761,62 @@
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>Different pack quantity</t>
+          <t>Identical product name and details</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Treatment</t>
+          <t>Luxatemp Automix Plus Mix Tips (DMG) | Dental Product</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Safco Dental Supply</t>
+          <t>Pearson Dental Supply</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/3m-sup-trade-sup-clinpro-sup-trade-sup-clear-fluoride-treatment</t>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13577&amp;catid=7775&amp;subcatid=22416&amp;pid=73558&amp;page=1</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>137.49</v>
+        <v>68.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>pack quantity is 1, not 25</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -2939,43 +2835,45 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Different variant (mint flavor)</t>
+          <t>Different variant and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Clear Fluoride Treatment, No Flavor, 0.5mL Unit ...</t>
+          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Atlanta Dental Supply</t>
+          <t>Patterson Dental</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>https://atlantadental.com/dental-supplies/product/45097210FF</t>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
         </is>
       </c>
       <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
+      <c r="G37" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2998,41 +2896,41 @@
       <c r="O37" s="9" t="inlineStr"/>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 278.99</t>
+          <t>price None failed sanity vs Schein unit 82.19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Safco CleanCare disposable prophy angles</t>
+          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Safco Dental Supply</t>
+          <t>MVP Dental Supply</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
+          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>26.99</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -3041,240 +2939,220 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Marketing-name variation of the same product line</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
+          <t>Side-by-side comparison of Impression Material Mixing Tips</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Dentalcompare.com</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>500</v>
-      </c>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4803-Impression-Material-Mixing-Tips/Compare/?compare=3282424%2C3282425%2C3282426&amp;catid=4803</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N39" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O39" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L39" s="9" t="inlineStr"/>
+      <c r="M39" s="9" t="inlineStr"/>
+      <c r="N39" s="9" t="inlineStr"/>
+      <c r="O39" s="9" t="inlineStr"/>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Prophy Angles</t>
+          <t>Denture Boxes, Assorted, 12/bx</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/exam-hygiene/prophylaxis/prophy-angles/</t>
+          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>152.99</v>
+        <v>5.99</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>pack quantity is 200, not 500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Different product name and pack quantity</t>
+          <t>Exact match in name, brand, size/form, and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
+          <t>Denture Storage Boxes, Assorted, 12/Pk | 100010</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
+          <t>https://www.supplyclinic.com/items/denture-storage-boxes-assorted-12-pk-hsb-house-brand-dentistry-100010</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>263.85</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Add $10 for free shipping from Frontier Dental Supply Inc.</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -3294,42 +3172,40 @@
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>Exact match in name, brand, size/form, and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
+          <t>Denture Box - 12 Pack</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Zirc Dental Products</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
+          <t>https://zirc.com/products/denture-box</t>
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>355.09</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>500</v>
-      </c>
+        <v>16.5</v>
+      </c>
+      <c r="G42" s="5" t="n"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3337,69 +3213,57 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product family and variant is similar</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Introducing ACCLEAN Disposable Prophy Angles</t>
+          <t>Denture Storage Boxes</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Dental Product Shopper</t>
+          <t>Keystone Industries</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalproductshopper.com/blog/enhancing-dental-care--introducing-acclean-disposable-prophy-angles</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
+          <t>https://dental.keystoneindustries.com/product/denture-storage-boxes/</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>120</v>
+      </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3422,40 +3286,42 @@
       <c r="O43" s="9" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 222.77</t>
+          <t>price 140.45 failed sanity vs Schein unit 29.46</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Supplies for mixing paints - Painting and airbrushing</t>
+          <t>Denture Boxes 12/Pack</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Finescale Modeler Forum</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>https://forum.finescale.com/t/supplies-for-mixing-paints/242548</t>
+          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="G44" s="5" t="n"/>
+        <v>11.17</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3463,69 +3329,69 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K44" s="5" t="n">
         <v>100</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Completely unrelated product</t>
+          <t>Exact match in name, brand, size/form, and pack quantity. Disagreement between title and scraped_product_name, but scraped_product_name confirms the match</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Perfectemp Blue Mixing Tips Pack of 25</t>
+          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>Cam Supply</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/4845-527/perfectemp-blue-mixing-tips-pack-of-25</t>
+          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>27.19</v>
+        <v>15</v>
       </c>
       <c r="G45" s="9" t="n"/>
       <c r="H45" s="10" t="inlineStr">
@@ -3535,7 +3401,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
@@ -3550,42 +3416,40 @@
       <c r="O45" s="9" t="inlineStr"/>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
+          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Darkside Tattoo Supply Inc</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
+          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>25</v>
-      </c>
+        <v>15.25</v>
+      </c>
+      <c r="G46" s="5" t="n"/>
       <c r="H46" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3593,73 +3457,55 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Marketing-name variation, same product line</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>3D Essentials Barrier Film Blue 4X6 1200/Roll | BARB</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
+          <t>https://www.supplyclinic.com/items/3d-essentials-barrier-film-blue-4x6-1200-roll-3d-dental-barb</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>64.93000000000001</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>25</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G47" s="9" t="n"/>
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3667,55 +3513,39 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L47" s="9" t="inlineStr"/>
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr"/>
+      <c r="O47" s="9" t="inlineStr"/>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Core Material Mixing &amp; Applicator Tips</t>
+          <t>Primo 4" x 6" Barrier Film, Blue. Roll of 1200 Sheets. Non- ...</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3725,89 +3555,69 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/core-material-mixing-applicator-tips-l-532-219962</t>
+          <t>https://www.net32.com/ec/primo-4-x-6-barrier-film-blue-d-162058</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>40</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G48" s="5" t="n"/>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Larger pack</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Different product and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
+          <t>Dukal Barrier Film, Blue, 4" x 6" Sheet, 1200 sheets/Roll ...</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>The Dental Market U.S.</t>
+          <t>Global Industrial</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>https://thedentalmarket.net/featured-items/luxatemp-automix-plus-fine-mixing-tips-box-of-25/</t>
+          <t>https://www.globalindustrial.com/p/barrier-film-blue-4-x-6-sheet-1200-sheets-roll-12-rolls-case</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>64.95</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>25</v>
-      </c>
+        <v>239.95</v>
+      </c>
+      <c r="G49" s="9" t="n"/>
       <c r="H49" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3815,71 +3625,57 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M49" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N49" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O49" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L49" s="9" t="inlineStr"/>
+      <c r="M49" s="9" t="inlineStr"/>
+      <c r="N49" s="9" t="inlineStr"/>
+      <c r="O49" s="9" t="inlineStr"/>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>Marketing-name variation, same product line</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus</t>
+          <t>JMU Dental Barrier Film 4"x6" – 1200 Sheets/Roll, Self ...</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>JMU Dental</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
+          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>449.95</v>
-      </c>
-      <c r="G50" s="5" t="n"/>
+        <v>6.99</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>1200</v>
+      </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3891,35 +3687,51 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different variant (Clear vs Blue)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
+          <t>Barrier Film 4x6 1200 Sheets Blue | KY100Z</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -3929,30 +3741,30 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+          <t>https://www.supplyclinic.com/items/barrier-film-4x6-1200-sheets-blue-sky-dental-supply-ky100z</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>58.27</v>
+        <v>10.5</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Add $200 for free shipping from Sky Dental Supply</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
@@ -3961,7 +3773,7 @@
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N51" s="9" t="inlineStr">
@@ -3976,106 +3788,124 @@
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Light Blue instead of Fine)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
+          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Patterson Dental</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="n"/>
+          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>11.99</v>
+      </c>
       <c r="G52" s="5" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 82.19</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
+          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>MVP Dental Supply</t>
+          <t>Dental Mates</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
+          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>75.04000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>25</v>
+        <v>1200</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>One Roll or 8 Rolls Case</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
@@ -4106,41 +3936,41 @@
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>Marketing-name variation, same product line</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes, Assorted, 12/bx</t>
+          <t>Dental City - Barrier Film 4x6 Perforated Sheets</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+          <t>https://www.dentalcity.com/product/17348/dental-city-barrier-film-4x6-perforated-sheets</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>5.99</v>
+        <v>16.49</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
@@ -4153,10 +3983,10 @@
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -4180,57 +4010,57 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Includes dispenser box</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Denture Box - 12 Pack</t>
+          <t>Essentials 4" x 6" Barrier Film, Blue, 1200/Pk</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Zirc Dental Products</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>https://zirc.com/products/denture-box</t>
+          <t>https://www.net32.com/ec/essentials-4-x-6-barrier-film-blue-d-188821</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>16.5</v>
+        <v>15.46</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Unavailable</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
@@ -4239,7 +4069,7 @@
       </c>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N55" s="9" t="inlineStr">
@@ -4254,45 +4084,45 @@
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Midnight Blue vs Assorted)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Zirc Personalized Denture Boxes 12/Pack</t>
+          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/zirc-personalized-denture-boxes-12-pack/p/70297185</t>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>21.59</v>
+        <v>97</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>12</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>None specified</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -4301,10 +4131,10 @@
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
@@ -4328,57 +4158,57 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Assorted Colors with optional imprint lines vs Assorted) and marketing name variation</t>
+          <t>Different product name, but same product family</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Essentials Denture Box, Assorted Colors, 12/Pk</t>
+          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal ...</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Broward A&amp;C Medical Supply</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/essentials-denture-box-assorted-colors-12-pk-d-188852</t>
+          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>14.91</v>
+        <v>118</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Standard Shipping: $5.95</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
@@ -4387,7 +4217,7 @@
       </c>
       <c r="M57" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N57" s="9" t="inlineStr">
@@ -4402,42 +4232,40 @@
       </c>
       <c r="P57" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different product name, but same product family</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Dental City - Denture Boxes 12/Pack</t>
+          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/9911/dental-city-denture-boxes-12pack</t>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>12</v>
-      </c>
+        <v>140.08</v>
+      </c>
+      <c r="G58" s="5" t="n"/>
       <c r="H58" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -4445,92 +4273,76 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr"/>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Title and scraped product name disagree, but scraped product name is authoritative</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>PLASDENT # 200BTH-XA - DENTURE BOXES</t>
+          <t>Axess Nasal Mask, Medium, Unscented, 24/bx, Low profile, ...</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/plasdent-denture-box-assorted-chr-plasdent-200bth-xa</t>
+          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>8.18</v>
+        <v>161.2</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Larger pack/case</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
@@ -4545,47 +4357,43 @@
       </c>
       <c r="O59" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Chroma Colored vs Assorted)</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>The Essentials Denture Boxes Assorted 12/Pk</t>
+          <t>Silhouette 2 Low Profile Nasal Masks Medium 12/pack</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Dental Health Products</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Dent-Shur-Cups-MI400</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>12</v>
-      </c>
+          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
       <c r="H60" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -4593,146 +4401,110 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr"/>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film 4" x 6" Blue Roll of 1200 Sheets</t>
+          <t>Silhouette 2 Low Profile Nasal Mask, Adult, Small</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>Midwest Dental</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>https://pricenex.com/barrier-film-4-x-6-blue-roll-of-1200-sheets/</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>1200</v>
-      </c>
+          <t>https://midwestdental.com/adult-small-silhouette-masks-pk12</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Buy 5 - 9 at $4.85 each</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M61" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N61" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O61" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L61" s="9" t="inlineStr"/>
+      <c r="M61" s="9" t="inlineStr"/>
+      <c r="N61" s="9" t="inlineStr"/>
+      <c r="O61" s="9" t="inlineStr"/>
       <c r="P61" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>JMU Dental Barrier Film 4"x6" – 1200 Sheets/Roll, Self ...</t>
+          <t>ClearView Large Adult Nasal Masks 12/Pack</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>JMU Dental</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
+          <t>https://www.practicon.com/clearview-large-adult-nasal-masks-12-pack/p/704434</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>6.99</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1200</v>
+        <v>12</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -4745,14 +4517,14 @@
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -4772,45 +4544,45 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Variant mismatch: Blue vs Clear</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
+          <t>3cc Luer Lock Disposable Syringes (Non Sterile) (Box of 100)</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Darkside Tattoo Supply Inc</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
+          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>15.25</v>
+        <v>10.99</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Buy 8 for $12.88 each and save 16%</t>
+          <t>1/bx</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
@@ -4846,57 +4618,57 @@
       </c>
       <c r="P63" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exact match in product name, size, and pack quantity.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
+          <t>Exel 3cc Luer Lock Syringe with Needle | 100 Pack</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Dental Mates</t>
+          <t>Medical and Lab Supplies</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
+          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>9.99</v>
+        <v>20.95</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Pack quantity mismatch: 1 vs 1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
@@ -4905,7 +4677,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -4915,46 +4687,46 @@
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different variant (sterile vs non-sterile) and disagreement between title and scraped product name.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
+          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Cam Supply</t>
+          <t>Medex Supply</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
+          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>15</v>
+        <v>15.95</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
@@ -4963,14 +4735,14 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L65" s="9" t="inlineStr">
         <is>
@@ -4994,42 +4766,40 @@
       </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>Title and scraped product name mismatch</t>
+          <t>Exact match in product name, size, and pack quantity.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Primo 4" x 6" Barrier Film, Blue. Roll of 1200 Sheets. Non- ...</t>
+          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Bound Tree Medical</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/primo-4-x-6-barrier-film-blue-d-162058</t>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>1200</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G66" s="5" t="n"/>
       <c r="H66" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5037,81 +4807,63 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Dukal Barrier Film, Blue, 4" x 6" Sheet, 1200 sheets/Roll ...</t>
+          <t>3M™ Clinpro™ Sealant Refill 1.2ml Syringe</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Global Industrial</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>https://www.globalindustrial.com/p/barrier-film-blue-4-x-6-sheet-1200-sheets-roll-12-rolls-case</t>
+          <t>https://shop.benco.com/Product/3168-583/3m-clinpro-sealant-refill-12ml-syringe</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>239.95</v>
-      </c>
-      <c r="G67" s="9" t="n">
-        <v>12</v>
-      </c>
+        <v>43.49</v>
+      </c>
+      <c r="G67" s="9" t="n"/>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
@@ -5126,170 +4878,172 @@
       <c r="O67" s="9" t="inlineStr"/>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>price 239.95 failed sanity vs Schein unit 24.31</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
+          <t>iris® Pit and Fissure Sealant A2 1.2ml Syringe Pack of 4</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>skydentalsupply.com</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+          <t>https://shop.benco.com/Product/4006-862/iris-pit-and-fissure-sealant-a2-12ml-syringe-pack-</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>1200</v>
-      </c>
+        <v>77.98999999999999</v>
+      </c>
+      <c r="G68" s="5" t="n"/>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Minimal quantity for this product is 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O68" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr"/>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
+          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Tri County Dental Supply</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>140.08</v>
-      </c>
-      <c r="G69" s="9" t="n"/>
+        <v>25.95</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>includes 10 tips</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="9" t="inlineStr"/>
-      <c r="M69" s="9" t="inlineStr"/>
-      <c r="N69" s="9" t="inlineStr"/>
-      <c r="O69" s="9" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P69" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>disagreeing title and scraped_product_name, but same product family</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
+          <t>3M Clinpro Sealant Refill, Syringe</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Bound Tree Medical</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Treatments-%26-Prescription-Materials/Sealants/3M-Clinpro-Sealant-Refill%2C-Syringe/p/310009-101</t>
         </is>
       </c>
       <c r="F70" s="8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G70" s="5" t="n"/>
+        <v>30.29</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5297,53 +5051,69 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="5" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr"/>
-      <c r="O70" s="5" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>exact match, same product and packaging</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>3 mL Syringe without Needle</t>
+          <t>3M™ Clinpro™ Sealant</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Vitality Medical</t>
+          <t>Top Quality Manufacturing, LLC</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>https://www.vitalitymedical.com/3-ml-syringe-without-needle.html</t>
+          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>35.39</v>
+        <v>33.25</v>
       </c>
       <c r="G71" s="9" t="n"/>
       <c r="H71" s="10" t="inlineStr">
@@ -5375,50 +5145,50 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>3cc Luer Lock Disposable Syringes (Non Sterile) (Box of 100)</t>
+          <t>Clinpro Sealant Refill 1.2ml Syringe</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
+          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>10.99</v>
+        <v>29.77</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Backordered</t>
+          <t>includes 10 dispensing tips</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
@@ -5437,48 +5207,50 @@
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Exact match found</t>
+          <t>same product, but includes additional items</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Non-Sterile Luer-Lok Syringes, Bulk |BD</t>
+          <t>Prevent Seal Self-Etching Sealant 1.2ml</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>The Lab Depot</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>https://www.labdepotinc.com/bd-non-sterile-luer-lok-syringes-bulk</t>
+          <t>https://www.supplyclinic.com/items/prevent-seal-self-etching-sealant-1-2ml-itena-usa-pvseal-1-2</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>194.78</v>
-      </c>
-      <c r="G73" s="9" t="n"/>
+        <v>40.39</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4, Get 1 Free!</t>
         </is>
       </c>
       <c r="I73" s="9" t="inlineStr">
@@ -5487,54 +5259,72 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="9" t="inlineStr"/>
-      <c r="N73" s="9" t="inlineStr"/>
-      <c r="O73" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>different product, not Clinpro Sealant</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>BD Non-Sterile Syringes - Luer-Lock™ Tips</t>
+          <t>Clinpro Sealant</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Nelson-Jameson</t>
+          <t>Amtouch</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>https://nelsonjameson.com/bd-luer-lok-syringes-without-needle-3-ml-cc-non-sterile-1600-301073-148820.html</t>
+          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>270.63</v>
-      </c>
-      <c r="G74" s="5" t="n"/>
+        <v>8.220000000000001</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 x 6ml Sealant Bottles</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -5543,54 +5333,72 @@
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="5" t="inlineStr"/>
-      <c r="M74" s="5" t="inlineStr"/>
-      <c r="N74" s="5" t="inlineStr"/>
-      <c r="O74" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>price 270.63 failed sanity vs Schein unit 17.61</t>
+          <t>different product size and packaging</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>B-D Disposable Syringe, Non-Sterile, Luer-Lok, Bulk Pack, ...</t>
+          <t>3M Clinpro Sealant Introductory Kit, 12626, 1.2 mL/Syringe, ...</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Cole-Parmer</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>https://www.coleparmer.com/i/b-d-disposable-syringe-non-sterile-luer-lok-bulk-pack-3-ml-1600-cs/0794502</t>
+          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>340</v>
-      </c>
-      <c r="G75" s="9" t="n"/>
+        <v>89.81</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Introductory Kit, 2 Syringes/Kit</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -5599,18 +5407,34 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="9" t="inlineStr"/>
-      <c r="M75" s="9" t="inlineStr"/>
-      <c r="N75" s="9" t="inlineStr"/>
-      <c r="O75" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P75" s="10" t="inlineStr">
         <is>
-          <t>price 340.0 failed sanity vs Schein unit 17.61</t>
+          <t>different product, Introductory Kit</t>
         </is>
       </c>
     </row>
@@ -5627,23 +5451,23 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Sealant Introductory Kit, 12626, 1.2 mL/Syringe, ...</t>
+          <t>Dental Pit and Fissure Sealants</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Dentalcompare.com</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="n">
-        <v>17.54</v>
-      </c>
-      <c r="G76" s="5" t="n"/>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5666,98 +5490,80 @@
       <c r="O76" s="5" t="inlineStr"/>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>price None failed sanity vs Schein unit 32.2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
+          <t>PureVac SC Evacuation System Cleaner (Sultan)</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Tri County Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+          <t>https://www.skydentalsupply.com/purevac-sc-evac-cleaner-.htm</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="G77" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>24.99</v>
+      </c>
+      <c r="G77" s="9" t="n"/>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>includes 10 tips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M77" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N77" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O77" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr"/>
+      <c r="N77" s="9" t="inlineStr"/>
+      <c r="O77" s="9" t="inlineStr"/>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>disagreement between title and scraped_product_name</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Eco-S Pit &amp; Fissure Sealant - Sealant Refill: 4 - 1.2 mL ...</t>
+          <t>Purevac SC Evacuation System Cleaner, Citrus scent</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5767,162 +5573,150 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/ecos-pit-fissure-sealant-refill-4-12-d-54050</t>
+          <t>https://www.net32.com/ec/purevac-sc-evacuation-system-cleaner-5-liter169-d-143563</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>31.83</v>
+        <v>170.37</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>4 syringes and 20 needle tips</t>
+          <t>larger pack/case</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O78" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N78" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O78" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>different brand and product name</t>
+          <t>Different scent (Citrus) and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant – 1.2 ml Syringe Refill</t>
+          <t>Purevac SC Evacuation System Cleaner</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>inpiXel Store</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>https://inpixelstore.com/product/clinpro-sealant-1-2-ml-syringe-refill/</t>
+          <t>https://www.scottsdental.com/purevac-sc.html</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="G79" s="9" t="n"/>
+        <v>76.95</v>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4 Get 1 FREE!</t>
         </is>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M79" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N79" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O79" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L79" s="9" t="inlineStr"/>
+      <c r="M79" s="9" t="inlineStr"/>
+      <c r="N79" s="9" t="inlineStr"/>
+      <c r="O79" s="9" t="inlineStr"/>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>missing scraped_product_name and scraped_variant</t>
+          <t>volume/size mismatch after normalization</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>3M™ Clinpro™ Sealant Refill 1.2ml Syringe</t>
+          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/3168-583/3m-clinpro-sealant-refill-12ml-syringe</t>
+          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="G80" s="5" t="n"/>
+        <v>194.45</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -5958,39 +5752,37 @@
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>exact match, but missing scraped_product_name and scraped_variant</t>
+          <t>Exact match, same product and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant</t>
+          <t>PUREVAC SC Evacuation System Cleaner 5 Liters</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Amtouch</t>
+          <t>Dental Health Products, Inc.</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>116.18</v>
-      </c>
+          <t>https://www.dhpsupply.com/item/550-21135/PUREVAC-SC-Evacuation-System/</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="n"/>
       <c r="G81" s="9" t="n"/>
       <c r="H81" s="10" t="inlineStr">
         <is>
@@ -6014,425 +5806,7 @@
       <c r="O81" s="9" t="inlineStr"/>
       <c r="P81" s="10" t="inlineStr">
         <is>
-          <t>price 116.18 failed sanity vs Schein unit 32.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Refill 1.2ml Syringe</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Crazy Dental Price Club</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="n">
-        <v>354.99</v>
-      </c>
-      <c r="G82" s="5" t="n"/>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr"/>
-      <c r="O82" s="5" t="inlineStr"/>
-      <c r="P82" s="6" t="inlineStr">
-        <is>
-          <t>price 354.99 failed sanity vs Schein unit 32.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>3M™ Clinpro™ Sealant</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>Top Quality Manufacturing, LLC</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>403.05</v>
-      </c>
-      <c r="G83" s="9" t="n"/>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="9" t="inlineStr"/>
-      <c r="M83" s="9" t="inlineStr"/>
-      <c r="N83" s="9" t="inlineStr"/>
-      <c r="O83" s="9" t="inlineStr"/>
-      <c r="P83" s="10" t="inlineStr">
-        <is>
-          <t>price 403.05 failed sanity vs Schein unit 32.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Evacuation System Cleaners - Sky Dental Supply</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>skydentalsupply.com</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/evac-cleaner/</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N84" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O84" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P84" s="6" t="inlineStr">
-        <is>
-          <t>No product information available</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation System Cleaner, Citrus scent</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>Net32</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/purevac-sc-evacuation-system-cleaner-5-liter169-d-143563</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K85" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M85" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N85" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O85" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P85" s="10" t="inlineStr">
-        <is>
-          <t>Different variant (citrus scent), but same product family</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation System Cleaner</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Scott's Dental Supply</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>https://www.scottsdental.com/purevac-sc.html</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="5" t="inlineStr"/>
-      <c r="M86" s="5" t="inlineStr"/>
-      <c r="N86" s="5" t="inlineStr"/>
-      <c r="O86" s="5" t="inlineStr"/>
-      <c r="P86" s="6" t="inlineStr">
-        <is>
-          <t>price None failed sanity vs Schein unit 144.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>US Dental Depot</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="n"/>
-      <c r="G87" s="9" t="n"/>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="9" t="inlineStr"/>
-      <c r="M87" s="9" t="inlineStr"/>
-      <c r="N87" s="9" t="inlineStr"/>
-      <c r="O87" s="9" t="inlineStr"/>
-      <c r="P87" s="10" t="inlineStr">
-        <is>
-          <t>price None failed sanity vs Schein unit 144.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>Purevac® SC Evacuation System Cleaner - 2 Liter</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Patterson Dental</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="5" t="inlineStr"/>
-      <c r="M88" s="5" t="inlineStr"/>
-      <c r="N88" s="5" t="inlineStr"/>
-      <c r="O88" s="5" t="inlineStr"/>
-      <c r="P88" s="6" t="inlineStr">
-        <is>
-          <t>price None failed sanity vs Schein unit 144.39</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -6460,73 +5834,64 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6636,7 +6001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6685,7 +6050,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>https://www.henryscheindental.com/us-en/shopping/products.aspx?productid=5700366%2C5700362%2C5700361%2C5700344%2C5700363%2C5700365%2C5700360&amp;PromoCode=TEM&amp;cdivid=international_d</t>
+          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -6697,12 +6062,12 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>5700360</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4803-Impression-Material-Mixing-Tips/Compare/?compare=3282424%2C3282425%2C3282426&amp;catid=4803</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -6714,12 +6079,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
+          <t>https://zirc.com/products/denture-box</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -6731,12 +6096,12 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -6748,12 +6113,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
+          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -6765,12 +6130,12 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
+          <t>https://midwestdental.com/adult-small-silhouette-masks-pk12</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -6782,12 +6147,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/4845-527/perfectemp-blue-mixing-tips-pack-of-25</t>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6799,12 +6164,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
+          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -6816,12 +6181,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+          <t>https://www.skydentalsupply.com/purevac-sc-evac-cleaner-.htm</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -6833,66 +6198,15 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+          <t>https://www.dhpsupply.com/item/550-21135/PUREVAC-SC-Evacuation-System/</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>5701400</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.vitalitymedical.com/3-ml-syringe-without-needle.html</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>5701400</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>https://www.labdepotinc.com/bd-non-sterile-luer-lok-syringes-bulk</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>login required for pricing (public pricing only)</t>
         </is>
@@ -6914,9 +6228,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6946,7 +6257,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parsed Order Audit  ·  tmp3s170sgz.pdf</t>
+          <t>Parsed Order Audit  ·  tmpvzi7wc3x.pdf</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7319,7 +6630,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Henry Schein</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -7407,7 +6718,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Porter</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">

--- a/output/OR202603121104075460_evidence.xlsx
+++ b/output/OR202603121104075460_evidence.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 16:46</t>
+          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 20:08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -655,21 +655,21 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel</t>
+          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
+          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
@@ -711,21 +711,21 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>ProJel-20, Cherry Flavor, 60 gm Jar. 20% Benzocaine ...</t>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/projel20-cherry-flavor-60-gm-jar-20-d-101965</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="10" t="inlineStr">
@@ -767,21 +767,21 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
+          <t>ProJel-20, Cherry Flavor, 60 gm Jar. 20% Benzocaine ...</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>zoro.com</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
+          <t>https://www.net32.com/ec/projel20-cherry-flavor-60-gm-jar-20-d-101965</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>11.59</v>
+        <v>7</v>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="inlineStr">
@@ -823,64 +823,46 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>House Brand Strawberry flavored Topical Anesthetic Gel ...</t>
+          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>zoro.com</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/house-brand-strawberry-flavored-topical-anesthetic-gel-d-78066</t>
+          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>11.59</v>
+      </c>
+      <c r="G7" s="9" t="n"/>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="9" t="inlineStr"/>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -897,64 +879,46 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>House Brand Strawberry Flavored Topical Anesthetic Gel ( ...</t>
+          <t>Benzo-Jel Topical Anesthetic Gel Strawberry 1oz/Jr</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
+          <t>https://www.supplyclinic.com/items/benzo-jel-topical-anesthetic-gel-strawberry-1oz-jr-henry-schein-inc-03-32019</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>25.59</v>
+      </c>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Free Shipping on $100+ Orders</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -971,28 +935,28 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
+          <t>Opahl Topical Anesthetic Gel 20% Benzocaine</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>iSmile Dental Products</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
+          <t>https://www.net32.com/ec/opahl-topical-anesthetic-gel-20-benzocaine-raspberry-d-131159</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>4.99</v>
+        <v>2.97</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>6 for $4.49 each (10% discount)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1045,28 +1009,28 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
+          <t>Topical Anesthetic Gel Strawberry 1oz.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Davis Dental Supply</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
+          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>Re-stocking soon</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1075,10 +1039,10 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -1102,7 +1066,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>No brand mentioned and different product name</t>
         </is>
       </c>
     </row>
@@ -1119,20 +1083,22 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel Strawberry 1oz/Jr</t>
+          <t>House Brand Strawberry Flavored Topical Anesthetic Gel ( ...</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>SurgiMac Dental Supply</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/benzo-jel-topical-anesthetic-gel-strawberry-1oz-jr-henry-schein-inc-03-32019</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n"/>
+          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>3.99</v>
+      </c>
       <c r="G11" s="9" t="n">
         <v>1</v>
       </c>
@@ -1147,18 +1113,34 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="9" t="inlineStr"/>
-      <c r="N11" s="9" t="inlineStr"/>
-      <c r="O11" s="9" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 6.29</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1175,49 +1157,49 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel</t>
+          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>iSmile Dental Products</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>6.5</v>
+        <v>4.99</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>1/each</t>
+          <t>Buy 6 for $4.49 each with 10% discount</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -1232,7 +1214,7 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Exact match</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1249,21 +1231,25 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>GEL 1 OZ. BTL STRAWBERRY | PRO-LINE # 018-024</t>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-5</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -1271,54 +1257,68 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr"/>
-      <c r="N13" s="9" t="inlineStr"/>
-      <c r="O13" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Matching brand, product name, size, and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>5700360</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
+          <t>Dental Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Dental Health Products, Inc.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>234</v>
-      </c>
+          <t>https://www.dhpsupply.com/item/120-320062/DHP-Topical-Anesthetic-Gel/</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
@@ -1342,42 +1342,38 @@
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>5700360</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
+          <t>GEL 1 OZ. BTL STRAWBERRY | PRO-LINE # 018-024</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>48</v>
-      </c>
+          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
       <c r="H15" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -1389,34 +1385,18 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr"/>
+      <c r="N15" s="9" t="inlineStr"/>
+      <c r="O15" s="9" t="inlineStr"/>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -1433,25 +1413,23 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
+          <t>Maxima HP High Performance Mixing</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>48</v>
-      </c>
+        <v>66.06999999999999</v>
+      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -1459,38 +1437,22 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Different product variant and size</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -1507,25 +1469,23 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Practicon HP Universal Mixing Tips, Yellow 4.2mm, Pack of 48</t>
+          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>jobs.pfefferwerk.de</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>https://jobs.pfefferwerk.de/products/practicon-hp-universal-mixing-tips-yellow-42mm-pack-of-48</t>
+          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>48</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="G17" s="9" t="n"/>
       <c r="H17" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -1533,38 +1493,22 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr"/>
+      <c r="N17" s="9" t="inlineStr"/>
+      <c r="O17" s="9" t="inlineStr"/>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but similar product name and variant</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -1581,21 +1525,21 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Maxima HP High Performance Mixing</t>
+          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
+          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>39.73</v>
+        <v>23.86</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>48</v>
@@ -1607,23 +1551,23 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -1638,7 +1582,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Same brand and product name, but variant description is incomplete</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1655,21 +1599,21 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Mixing Tips HP Yellow 4.2mm 48/Bag</t>
+          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/15798/dental-city-mixing-tips-hp-yellow-42mm-48bag</t>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>40.13</v>
+        <v>5.95</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>48</v>
@@ -1685,10 +1629,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
@@ -1702,7 +1646,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -1712,7 +1656,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Different product variant and size</t>
         </is>
       </c>
     </row>
@@ -1729,40 +1673,40 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>HP Mixing Tips, 4.2 mm, Yellow, 48/Pk, 100623</t>
+          <t>Mixing Tips HP Yellow 4.2mm 48/Bag</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524</t>
+          <t>https://www.dentalcity.com/product/15798/dental-city-mixing-tips-hp-yellow-42mm-48bag</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>42.99</v>
+        <v>40.13</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Larger pack size</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -1771,7 +1715,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -1781,12 +1725,12 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Different product name and pack quantity, scraped product name does not match title</t>
+          <t>Different brand, but same product name and variant</t>
         </is>
       </c>
     </row>
@@ -1803,40 +1747,40 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>MARK3 HIGH PERFORMANCE MIXING TIPS</t>
+          <t>High Performance Mixing Tips Yellow 4.2mm</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>Pearsonlab.com</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+          <t>https://www.pearsonlab.com/catalog/product.asp?majcatid=4547&amp;catid=7084&amp;subcatid=72363&amp;pid=76855&amp;page=1</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>19.12</v>
+        <v>35.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
@@ -1845,7 +1789,7 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1855,152 +1799,190 @@
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>Different brand, product name, and pack quantity</t>
+          <t>Different brand, but same product name and variant</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>1126863</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>— no public candidates found —</t>
+          <t>HP Mixing Tips, 4.2 mm, Yellow, 48/Pk, 100623</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>2-pack price (ordered pack: 48)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different product and pack quantity, title and scraped product name disagree</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>1126863</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>— no public candidates found —</t>
+          <t>MARK3 HIGH PERFORMANCE MIXING TIPS</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>US Dental Depot</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Larger pack/case</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr"/>
-      <c r="N23" s="9" t="inlineStr"/>
-      <c r="O23" s="9" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different brand and pack quantity, but same product name and variant</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>1126863</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Prophy Angles</t>
+          <t>Mixing Tips 4.2 mm Yellow Bag of 50</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/exam-hygiene/prophylaxis/prophy-angles/</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>236.99</v>
-      </c>
+          <t>https://shop.benco.com/Product/6094-559/mixing-tips-42-mm-yellow-bag-of-50?Source=Similar.Proton</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -2009,7 +1991,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
@@ -2024,131 +2006,131 @@
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
+          <t>Oral-B Glide Pro-Health Healthy Gums Floss, 160M</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
+          <t>https://www.net32.com/ec/oralb-glide-prohealth-healthy-gums-floss-160m-d-184088</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>355.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack quantity</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>Different brand and variant</t>
+          <t>Different product variant (Pro-Health Healthy Gums) and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>ACCLEAN by Henry Schein | Prophy Angles</t>
+          <t>Oral-B Glide Healthy Gums Floss Refill 160m 2/Bx ...</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>71.86</v>
+        <v>11.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
@@ -2157,7 +2139,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -2167,47 +2149,45 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Different product name and pack quantity</t>
+          <t>Exact match with reference product</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
+          <t>Oral-B Glide Healthy Gums Floss 160M Refill Unflavored ...</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
+          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>263.85</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>500</v>
-      </c>
+        <v>14.29</v>
+      </c>
+      <c r="G27" s="9" t="n"/>
       <c r="H27" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2219,72 +2199,56 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O27" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
+      <c r="O27" s="9" t="inlineStr"/>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
+          <t>Oral-B® Glide Healthy Gums Floss with Dispenser 160m</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
+          <t>https://www.practicon.com/glide-pro-health-original-floss-160m-with-dispenser/p/71016231</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>153.9</v>
+        <v>12.59</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>Smaller pack quantity and includes dispenser</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2293,21 +2257,21 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2315,101 +2279,121 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product family</t>
+          <t>Different product variant (with dispenser) and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>5703169</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Acclean Disposable Prophy Angles Review | score: 4</t>
+          <t>Oral-B Glide Healthy Gums Unwaxed Teflon Floss 160 ...</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Dental Product Shopper</t>
+          <t>Dental Wholesale Direct</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalproductshopper.com/hygiene-preventive/prophy-angles/acclean-disposable-prophy-angles/evaluation</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="n"/>
+          <t>https://dentalwholesaledirect.com/preventives/oral-b-glide-healthy-gums-unwaxed-teflon-floss-160-meters-ea/</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>11.95</v>
+      </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack quantity</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
-      <c r="N29" s="9" t="inlineStr"/>
-      <c r="O29" s="9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 222.77</t>
+          <t>Different product variant (unwaxed Teflon) and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
+          <t>Maxill E-Z Slide max PACK 218 yd Waxed Floss ...</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+          <t>https://www.net32.com/ec/ez-slide-max-pack-218-yd-waxed-d-188208</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="G30" s="5" t="n"/>
+        <v>4.99</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -2417,55 +2401,73 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
+          <t>Preventives - Floss</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>The Dental Market U.S.</t>
+          <t>DDS Dental Supplies</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>https://thedentalmarket.net/featured-items/luxatemp-automix-plus-fine-mixing-tips-box-of-25/</t>
+          <t>https://ddsdentalsupplies.com/floss-5/</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="G31" s="9" t="n"/>
+        <v>5.69</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2473,113 +2475,143 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="9" t="inlineStr"/>
-      <c r="O31" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus</t>
+          <t>Intenso Mouthwash - 500ml Anti-Cavity Freshness</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>SurgiMac Dental Supply</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
+          <t>https://surgimac.com/products/fazzet-intenso-anti-cavity-mouthwash-x-500ml</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>449.95</v>
-      </c>
-      <c r="G32" s="5" t="n"/>
+        <v>5.99</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1-pack price (ordered pack: 2)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Completely different product (mouthwash)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Impression Mixing Tips</t>
+          <t>Oral-B Glide Healthy Gums Floss 160m Disp Vial 1/Bx ...</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>UC Dental Products</t>
+          <t>D C Dental Supply</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>http://www.ucdpi.com/impression-materials/mixing-tips.htm</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>25</v>
-      </c>
+          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2591,142 +2623,110 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr"/>
+      <c r="M33" s="9" t="inlineStr"/>
+      <c r="N33" s="9" t="inlineStr"/>
+      <c r="O33" s="9" t="inlineStr"/>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>Different product name and brand</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
+          <t>Ivory Toothbrush Cap for Hygiene</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>SurgiMac Dental Supply</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
+          <t>https://surgimac.com/products/toothbrush-cap-ivory-438</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>64.89</v>
+        <v>123.99</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free Shipping on $100+ Orders</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Marketing-name variation of the same product line</t>
+          <t>price 123.99 failed sanity vs Schein unit 16.62</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>Oral-B Glide Healthy Gums Floss 160M Refill unflavored, 2 ...</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
+          <t>https://admin.frontierdental.com/us/en/product/oral-b-glide-healthy-gums-floss-160m-refill-unflavored-2-count-replaces-proc-80303244-239653</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>64.93000000000001</v>
+        <v>14.04</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -2766,45 +2766,45 @@
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>Identical product name and details</t>
+          <t>Exact match with reference product</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Mix Tips (DMG) | Dental Product</t>
+          <t>Clinpro Clear 2.1% Sodium Fluoride Treatment, 0.5</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Pearson Dental Supply</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13577&amp;catid=7775&amp;subcatid=22416&amp;pid=73558&amp;page=1</t>
+          <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182709</t>
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>68.8</v>
+        <v>267.97</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>pack quantity is 1, not 25</t>
+          <t>1 @ $267.97,  2 @ $256.98</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -2835,44 +2835,46 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Different variant and pack quantity</t>
+          <t>Different flavor (Watermelon vs No Flavor)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
+          <t>LOCATOR Replacement Denture Cap Male Assembly, 10/Pk</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Patterson Dental</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="n"/>
+          <t>https://www.net32.com/ec/locator-replacement-denture-cap-male-assembly-10-d-178963</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>182.99</v>
+      </c>
       <c r="G37" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
@@ -2885,53 +2887,67 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="9" t="inlineStr"/>
-      <c r="M37" s="9" t="inlineStr"/>
-      <c r="N37" s="9" t="inlineStr"/>
-      <c r="O37" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 82.19</t>
+          <t>Completely different product</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
+          <t>Clinpro™ In Office 2.1% NaF Clear Fluoride Treatment</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>MVP Dental Supply</t>
+          <t>Top Quality Manufacturing, LLC</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
+          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>25</v>
-      </c>
+        <v>285.99</v>
+      </c>
+      <c r="G38" s="5" t="n"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -2939,142 +2955,146 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Marketing-name variation of the same product line</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Side-by-side comparison of Impression Material Mixing Tips</t>
+          <t>3M - Clinpro Clear Fluoride Varnish 100/Pack</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Dentalcompare.com</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcompare.com/Restorative-Dentistry/4803-Impression-Material-Mixing-Tips/Compare/?compare=3282424%2C3282425%2C3282426&amp;catid=4803</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
+          <t>https://www.dentalcity.com/product/21837/3m-clinpro-clear-fluoride-varnish-100pack</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>100</v>
+      </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4, Get 1 Free</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="9" t="inlineStr"/>
-      <c r="M39" s="9" t="inlineStr"/>
-      <c r="N39" s="9" t="inlineStr"/>
-      <c r="O39" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N39" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different flavor (Mint vs No Flavor)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes, Assorted, 12/bx</t>
+          <t>3M Clinpro Clear Fluoride Treatment</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+          <t>https://www.scottsdental.com/3m-clinpro-clear-fluoride-treatment.html</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>5.99</v>
+        <v>133.95</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
@@ -3093,62 +3113,62 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Exact match in name, brand, size/form, and pack quantity</t>
+          <t>Different pack quantity (50 vs 100) and flavor (Mint vs No Flavor)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Denture Storage Boxes, Assorted, 12/Pk | 100010</t>
+          <t>3M Clinpro Clear Fluoride Treatment</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Safco Dental Supply</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/denture-storage-boxes-assorted-12-pk-hsb-house-brand-dentistry-100010</t>
+          <t>https://www.safcodental.com/product/3m-sup-trade-sup-clinpro-sup-trade-sup-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>9.029999999999999</v>
+        <v>272.99</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Add $10 for free shipping from Frontier Dental Supply Inc.</t>
+          <t>No minimum order condition listed.</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
@@ -3172,39 +3192,37 @@
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>Exact match in name, brand, size/form, and pack quantity</t>
+          <t>Different flavor (Mint vs No Flavor)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Denture Box - 12 Pack</t>
+          <t>3M™ Clinpro™ Clear Fluoride Treatment Mint Flavor 0.5 ...</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Zirc Dental Products</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>https://zirc.com/products/denture-box</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>16.5</v>
-      </c>
+          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
@@ -3235,35 +3253,33 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Denture Storage Boxes</t>
+          <t>2pro Total Access Prophy Angle with Soft/Short Purple Cup ...</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Keystone Industries</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>https://dental.keystoneindustries.com/product/denture-storage-boxes/</t>
+          <t>https://www.net32.com/ec/2pro-total-access-prophy-angle-soft-short-d-100976</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>140.45</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>120</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G43" s="9" t="n"/>
       <c r="H43" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3271,7 +3287,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
@@ -3286,42 +3302,40 @@
       <c r="O43" s="9" t="inlineStr"/>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>price 140.45 failed sanity vs Schein unit 29.46</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes Assorted Assorted 12/Pk</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes 12/Pack</t>
+          <t>MARK3 Disposable Prophy Angle with SOFT GREEN CUP</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
+          <t>https://www.net32.com/ec/mark3-disposable-prophy-angle-soft-green-cup-d-155690</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>12</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G44" s="5" t="n"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3329,71 +3343,57 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J44" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Exact match in name, brand, size/form, and pack quantity. Disagreement between title and scraped_product_name, but scraped_product_name confirms the match</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
+          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Cam Supply</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
+          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="G45" s="9" t="n"/>
+        <v>355.09</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>500</v>
+      </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3401,111 +3401,147 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="9" t="inlineStr"/>
-      <c r="M45" s="9" t="inlineStr"/>
-      <c r="N45" s="9" t="inlineStr"/>
-      <c r="O45" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
+          <t>Safco CleanCare disposable prophy angles</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Darkside Tattoo Supply Inc</t>
+          <t>Safco Dental Supply</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
+          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="G46" s="5" t="n"/>
+        <v>26.99</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>3D Essentials Barrier Film Blue 4X6 1200/Roll | BARB</t>
+          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3d-essentials-barrier-film-blue-4x6-1200-roll-3d-dental-barb</t>
+          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G47" s="9" t="n"/>
+        <v>263.85</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>500</v>
+      </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3513,169 +3549,217 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="9" t="inlineStr"/>
-      <c r="O47" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Primo 4" x 6" Barrier Film, Blue. Roll of 1200 Sheets. Non- ...</t>
+          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/primo-4-x-6-barrier-film-blue-d-162058</t>
+          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>189</v>
-      </c>
-      <c r="G48" s="5" t="n"/>
+        <v>153.9</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>500</v>
+      </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Quantity discounts available</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand, but similar product name</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Dukal Barrier Film, Blue, 4" x 6" Sheet, 1200 sheets/Roll ...</t>
+          <t>ACCLEAN by Henry Schein | Prophy Angles</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Global Industrial</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>https://www.globalindustrial.com/p/barrier-film-blue-4-x-6-sheet-1200-sheets-roll-12-rolls-case</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>239.95</v>
-      </c>
-      <c r="G49" s="9" t="n"/>
+        <v>71.86</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>100</v>
+      </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="9" t="inlineStr"/>
-      <c r="M49" s="9" t="inlineStr"/>
-      <c r="N49" s="9" t="inlineStr"/>
-      <c r="O49" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different product name and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>JMU Dental Barrier Film 4"x6" – 1200 Sheets/Roll, Self ...</t>
+          <t>Acclean Disposable Prophy Angles Review | score: 4</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>JMU Dental</t>
+          <t>Dental Product Shopper</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>1200</v>
-      </c>
+          <t>https://www.dentalproductshopper.com/hygiene-preventive/prophy-angles/acclean-disposable-prophy-angles/evaluation</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
       <c r="H50" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3687,88 +3771,72 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Clear vs Blue)</t>
+          <t>price None failed sanity vs Schein unit 222.77</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film 4x6 1200 Sheets Blue | KY100Z</t>
+          <t>Perfect Choice Soft Prophy Angles Bulk 500/Box</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/barrier-film-4x6-1200-sheets-blue-sky-dental-supply-ky100z</t>
+          <t>https://www.practicon.com/perfect-choice-soft-prophy-angles-bulk-500-box/p/702938</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>10.5</v>
+        <v>177.29</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Add $200 for free shipping from Sky Dental Supply</t>
+          <t>No minimum order condition specified</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M51" s="9" t="inlineStr">
@@ -3788,190 +3856,152 @@
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different brand, but similar product name</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
+          <t>Luxatemp Ultra Smartmix - B1, 15 Gm. Syringe and 10 ...</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>skydentalsupply.com</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+          <t>https://www.net32.com/ec/luxatemp-ultra-smartmix-b1-15-gm-syringe-d-115709</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>1200</v>
-      </c>
+        <v>64.89</v>
+      </c>
+      <c r="G52" s="5" t="n"/>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr"/>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
+          <t>Luxatemp Automix Plus Mix Tips (DMG) | Dental Product</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Dental Mates</t>
+          <t>Pearson Dental Supply</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13577&amp;catid=7775&amp;subcatid=22416&amp;pid=73558&amp;page=1</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>1200</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="G53" s="9" t="n"/>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>One Roll or 8 Rolls Case</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L53" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M53" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N53" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O53" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L53" s="9" t="inlineStr"/>
+      <c r="M53" s="9" t="inlineStr"/>
+      <c r="N53" s="9" t="inlineStr"/>
+      <c r="O53" s="9" t="inlineStr"/>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Dental City - Barrier Film 4x6 Perforated Sheets</t>
+          <t>Crown &amp; Bridge - Temporary Material</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>DDS Dental Supplies</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/17348/dental-city-barrier-film-4x6-perforated-sheets</t>
+          <t>https://ddsdentalsupplies.com/temporary-material/</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>1200</v>
-      </c>
+        <v>96.34</v>
+      </c>
+      <c r="G54" s="5" t="n"/>
       <c r="H54" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3979,73 +4009,55 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Includes dispenser box</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>1469109</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Essentials 4" x 6" Barrier Film, Blue, 1200/Pk</t>
+          <t>Luxatemp Plus</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/essentials-4-x-6-barrier-film-blue-d-188821</t>
+          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>1200</v>
-      </c>
+        <v>449.95</v>
+      </c>
+      <c r="G55" s="9" t="n"/>
       <c r="H55" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -4053,72 +4065,56 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L55" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M55" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N55" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O55" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
+      <c r="M55" s="9" t="inlineStr"/>
+      <c r="N55" s="9" t="inlineStr"/>
+      <c r="O55" s="9" t="inlineStr"/>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
+          <t>Intra Oral Mixing Tips for Brown Tips 25 pcs/pk</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Anson Dental Supply</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
+          <t>https://ansondental.com/products/intra-oral-mixing-tips-for-brown-tips-25-pcs-pk</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>97</v>
+        <v>11.99</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
@@ -4127,18 +4123,18 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
@@ -4148,7 +4144,7 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -4158,61 +4154,61 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Different product name, but same product family</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal ...</t>
+          <t>Manufacturer Promotions | Save on Dental Brands</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Broward A&amp;C Medical Supply</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
+          <t>https://www.frontierdental.com/ca/en/manufacturer-promotions?banner_promo=eyJpdiI6Ik5LVm10bDdYcnpCb3F6TFRCVmJoZlE9PSIsInZhbHVlIjoieWFVbWZoWlY0NnROYzlSMGFCWkpVQT09IiwibWFjIjoiNWVhYmZmNzRkZmFhZGFiNGRlOGI2MDI0YmVkYzFmODBjMzVhNGNmYzU0MTZhZTY4Yjg1N2FhYzE2NzY3OWRiMSIsInRhZyI6IiJ9&amp;page=54</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>118</v>
+        <v>20.99</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack/case</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M57" s="9" t="inlineStr">
@@ -4222,53 +4218,55 @@
       </c>
       <c r="N57" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
         <is>
-          <t>Different product name, but same product family</t>
+          <t>Completely different product</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
+          <t>Manufacturer Promotions | Save on Dental Brands</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+          <t>https://www.frontierdental.com/ca/en/manufacturer-promotions?banner_promo=eyJpdiI6Ik5LVm10bDdYcnpCb3F6TFRCVmJoZlE9PSIsInZhbHVlIjoieWFVbWZoWlY0NnROYzlSMGFCWkpVQT09IiwibWFjIjoiNWVhYmZmNzRkZmFhZGFiNGRlOGI2MDI0YmVkYzFmODBjMzVhNGNmYzU0MTZhZTY4Yjg1N2FhYzE2NzY3OWRiMSIsInRhZyI6IiJ9&amp;page=14</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>140.08</v>
-      </c>
-      <c r="G58" s="5" t="n"/>
+        <v>20.99</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>500</v>
+      </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack/case</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -4277,56 +4275,72 @@
         </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Completely different product</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Axess Nasal Mask, Medium, Unscented, 24/bx, Low profile, ...</t>
+          <t>Dental Mixing Tips HP Blue-Orange - Pack Of 49 Disposable ...</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>oktowallz.com</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
+          <t>https://oktowallz.com/view/Orange-Pack-Of-49-Disposable-Tips-For-Dental-Impression/833810</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>161.2</v>
+        <v>13.99</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Larger pack/case</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
@@ -4335,7 +4349,7 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>90</v>
@@ -4352,7 +4366,7 @@
       </c>
       <c r="N59" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O59" s="9" t="inlineStr">
@@ -4362,38 +4376,42 @@
       </c>
       <c r="P59" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Different product and pack quantity</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Silhouette 2 Low Profile Nasal Masks Medium 12/pack</t>
+          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Dental Health Products</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
+          <t>https://www.net32.com/ec/luxatemp-automix-plus-fine-mixing-tips-25-d-45565</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>25</v>
+      </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -4401,110 +4419,146 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr"/>
-      <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Marketing-name variation of the same product line</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Silhouette 2 Low Profile Nasal Mask, Adult, Small</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Midwest Dental</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>https://midwestdental.com/adult-small-silhouette-masks-pk12</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
+          <t>https://www.crazydentalprices.com/Luxatemp-Automix-Plus-110351</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No Returns</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="9" t="inlineStr"/>
-      <c r="N61" s="9" t="inlineStr"/>
-      <c r="O61" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P61" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>ClearView Large Adult Nasal Masks 12/Pack</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/clearview-large-adult-nasal-masks-12-pack/p/704434</t>
+          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
         </is>
       </c>
       <c r="F62" s="8" t="n">
-        <v>98.98999999999999</v>
+        <v>58.27</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -4513,23 +4567,23 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
@@ -4544,115 +4598,95 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Different variant (Light Blue instead of Fine), but same product family</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>3cc Luer Lock Disposable Syringes (Non Sterile) (Box of 100)</t>
+          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Patterson Dental</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>100</v>
-      </c>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>1/bx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N63" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O63" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr"/>
+      <c r="O63" s="9" t="inlineStr"/>
       <c r="P63" s="10" t="inlineStr">
         <is>
-          <t>Exact match in product name, size, and pack quantity.</t>
+          <t>price None failed sanity vs Schein unit 82.19</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Exel 3cc Luer Lock Syringe with Needle | 100 Pack</t>
+          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Medical and Lab Supplies</t>
+          <t>MVP Dental Supply</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
+          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
         </is>
       </c>
       <c r="F64" s="8" t="n">
-        <v>20.95</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
@@ -4661,11 +4695,11 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>80</v>
@@ -4677,7 +4711,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -4692,42 +4726,40 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Different variant (sterile vs non-sterile) and disagreement between title and scraped product name.</t>
+          <t>Marketing-name variation of the same product line</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
+          <t>Denture Storage Boxes 12/Pk Red</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Medex Supply</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
+          <t>https://www.crazydentalprices.com/Denture-Storage-Boxes-9576660</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>100</v>
-      </c>
+        <v>15.65</v>
+      </c>
+      <c r="G65" s="9" t="n"/>
       <c r="H65" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -4735,69 +4767,53 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L65" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M65" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N65" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O65" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
+      <c r="O65" s="9" t="inlineStr"/>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>Exact match in product name, size, and pack quantity.</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
+          <t>Denture Box - 12 Pack</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Bound Tree Medical</t>
+          <t>Zirc Dental Products</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+          <t>https://zirc.com/products/denture-box</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="6" t="inlineStr">
@@ -4807,7 +4823,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J66" s="5" t="n">
@@ -4822,38 +4838,38 @@
       <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>3M™ Clinpro™ Sealant Refill 1.2ml Syringe</t>
+          <t>Oral-B Indicator Toothbrush 35 Soft Assorted Colors 12Bx</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>DDS Dental Supplies</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/3168-583/3m-clinpro-sealant-refill-12ml-syringe</t>
+          <t>https://ddsdentalsupplies.com/indicator-toothbrush-35-soft/</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>43.49</v>
+        <v>19.67</v>
       </c>
       <c r="G67" s="9" t="n"/>
       <c r="H67" s="10" t="inlineStr">
@@ -4885,31 +4901,31 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>iris® Pit and Fissure Sealant A2 1.2ml Syringe Pack of 4</t>
+          <t>New Age Denture Cases 12/Box</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/4006-862/iris-pit-and-fissure-sealant-a2-12ml-syringe-pack-</t>
+          <t>https://www.practicon.com/new-age-denture-cases-12-box/p/7017057</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>77.98999999999999</v>
+        <v>23.99</v>
       </c>
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="6" t="inlineStr">
@@ -4941,109 +4957,87 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
+          <t>Colorful Retainer Boxes - 12 Pack</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Tri County Dental Supply</t>
+          <t>SurgiMac Dental Supply</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+          <t>https://surgimac.com/products/retainer-boxes-assorted-colors-1430</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G69" s="9" t="n"/>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>includes 10 tips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M69" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N69" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O69" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr"/>
+      <c r="O69" s="9" t="inlineStr"/>
       <c r="P69" s="10" t="inlineStr">
         <is>
-          <t>disagreeing title and scraped_product_name, but same product family</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Sealant Refill, Syringe</t>
+          <t>Dental City - Denture Boxes 12/Pack</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Treatments-%26-Prescription-Materials/Sealants/3M-Clinpro-Sealant-Refill%2C-Syringe/p/310009-101</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>https://dentalcity.com/product/9911/dental-city-denture-boxes-12pack</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
       <c r="H70" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -5051,144 +5045,144 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N70" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O70" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr"/>
+      <c r="O70" s="5" t="inlineStr"/>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>exact match, same product and packaging</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>3M™ Clinpro™ Sealant</t>
+          <t>Denture Storage Boxes, Assorted, 12/Pk, 100010</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Top Quality Manufacturing, LLC</t>
+          <t>Frontier Dental Supply</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
+          <t>https://www.frontierdental.com/us/en/product/denture-storage-boxes-assorted-12pk-100010-161115</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="G71" s="9" t="n"/>
+        <v>7.85</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>This item requires special handling - a small fee will be applied once per order during checkout.</t>
         </is>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="9" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr"/>
-      <c r="N71" s="9" t="inlineStr"/>
-      <c r="O71" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P71" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Refill 1.2ml Syringe</t>
+          <t>House Brand Denture Boxes, Assorted, Box of 10</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
+          <t>/goto?url=CAESfwHuR6pNuLf0ElkSzuN5KPyNdhRISnExGL4KeUs5o-XYTKiprtrKYZIChSanekD2mxaVMqZz0dK4mcw6FJRK0Q4krLgB5jlEMXb5x_nMw4ZjZVe4WoIqMHaMc_I-jMlL0-rPUsglz362z423suwkgxUFjS_wGp0d3jmBD1J6ys4%3D</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>7.96</v>
+      </c>
+      <c r="G72" s="5" t="n"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>includes 10 dispensing tips</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
@@ -5197,12 +5191,12 @@
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
@@ -5212,66 +5206,66 @@
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>same product, but includes additional items</t>
+          <t>Insufficient data</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Prevent Seal Self-Etching Sealant 1.2ml</t>
+          <t>Denture Boxes, Assorted, 12/bx</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/prevent-seal-self-etching-sealant-1-2ml-itena-usa-pvseal-1-2</t>
+          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>40.39</v>
+        <v>5.99</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Buy 4, Get 1 Free!</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>100</v>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N73" s="9" t="inlineStr">
@@ -5286,45 +5280,45 @@
       </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>different product, not Clinpro Sealant</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant</t>
+          <t>Preventives</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Amtouch</t>
+          <t>DDS Dental Supplies</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
+          <t>https://ddsdentalsupplies.com/preventives/</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>8.220000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>2 x 6ml Sealant Bottles</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -5333,19 +5327,19 @@
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
@@ -5360,45 +5354,43 @@
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>different product size and packaging</t>
+          <t>Different product</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Sealant Introductory Kit, 12626, 1.2 mL/Syringe, ...</t>
+          <t>Essentials Denture Box, Assorted Colors, 12/Pk</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
+          <t>/goto?url=CAEShgEB7keqTYn8uUG8xfuZABXpIutatBQy3XaV36kpcgpmvQnQrGWoVSHwCUAPjmw8nRHGqhY_9iKU-2beQbgV1DvxyVQCIgFLtdzpOrfXBiJSnwoEs5OO88Pkx7YXJJx_e0kIHzAHMue35lsMbfQ1tPoYRICGp36P9oeKLjHbdP3AHZSl0mLTbQ%3D%3D</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>89.81</v>
-      </c>
-      <c r="G75" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>14.91</v>
+      </c>
+      <c r="G75" s="9" t="n"/>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Introductory Kit, 2 Syringes/Kit</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -5407,14 +5399,14 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
@@ -5424,7 +5416,7 @@
       </c>
       <c r="N75" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
@@ -5434,39 +5426,41 @@
       </c>
       <c r="P75" s="10" t="inlineStr">
         <is>
-          <t>different product, Introductory Kit</t>
+          <t>Insufficient data</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Dental Pit and Fissure Sealants</t>
+          <t>Denture Boxes 12/Pk Assorted | Guaranteed Lowest Price</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Dentalcompare.com</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="n"/>
+          <t>https://www.crazydentalprices.com/Denture-Boxes-30R800_2</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>15.4</v>
+      </c>
       <c r="G76" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
@@ -5475,55 +5469,73 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="5" t="inlineStr"/>
-      <c r="M76" s="5" t="inlineStr"/>
-      <c r="N76" s="5" t="inlineStr"/>
-      <c r="O76" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 32.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>PureVac SC Evacuation System Cleaner (Sultan)</t>
+          <t>Denture Boxes 12/Pack</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>skydentalsupply.com</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/purevac-sc-evac-cleaner-.htm</t>
+          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="G77" s="9" t="n"/>
+        <v>11.17</v>
+      </c>
+      <c r="G77" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -5531,72 +5543,88 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
-      <c r="N77" s="9" t="inlineStr"/>
-      <c r="O77" s="9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+          <t>Denture Boxes Assorted Assorted 12/Pk</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation System Cleaner, Citrus scent</t>
+          <t>PLASDENT # 200BTH-XA - DENTURE BOXES</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/purevac-sc-evacuation-system-cleaner-5-liter169-d-143563</t>
+          <t>https://usdentaldepot.com/plasdent-denture-box-assorted-chr-plasdent-200bth-xa</t>
         </is>
       </c>
       <c r="F78" s="8" t="n">
-        <v>170.37</v>
+        <v>8.18</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>larger pack/case</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
@@ -5605,7 +5633,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
@@ -5615,55 +5643,53 @@
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>Different scent (Citrus) and pack quantity</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation System Cleaner</t>
+          <t>Dukal Unipack Barrier Film - Infection Control</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>Optimus Dental Supply</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/purevac-sc.html</t>
+          <t>https://optimusdentalsupply.com/dukal-unipack-barrier-film/</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="G79" s="9" t="n">
-        <v>2</v>
-      </c>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="G79" s="9" t="n"/>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Buy 4 Get 1 FREE!</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
@@ -5678,111 +5704,95 @@
       <c r="O79" s="9" t="inlineStr"/>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>volume/size mismatch after normalization</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
+          <t>2026 Spring Savings</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>Pearson Dental Supply</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
+          <t>https://www.pearsondental.com/savings.asp</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>194.45</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>10.95</v>
+      </c>
+      <c r="G80" s="5" t="n"/>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N80" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O80" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
+      <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>Exact match, same product and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>1469109</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>PUREVAC SC Evacuation System Cleaner 5 Liters</t>
+          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Dental Health Products, Inc.</t>
+          <t>Darkside Tattoo Supply Inc</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/550-21135/PUREVAC-SC-Evacuation-System/</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="n"/>
+          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>12.88</v>
+      </c>
       <c r="G81" s="9" t="n"/>
       <c r="H81" s="10" t="inlineStr">
         <is>
@@ -5791,7 +5801,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
@@ -5805,6 +5815,3464 @@
       <c r="N81" s="9" t="inlineStr"/>
       <c r="O81" s="9" t="inlineStr"/>
       <c r="P81" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Dental Mates</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr"/>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>Cam Supply</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="9" t="inlineStr"/>
+      <c r="M83" s="9" t="inlineStr"/>
+      <c r="N83" s="9" t="inlineStr"/>
+      <c r="O83" s="9" t="inlineStr"/>
+      <c r="P83" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Dukal Unipack Barrier Film UBC-8045</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Optimus Dental Supply</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>https://optimusdentalsupply.com/dukal-unipack-barrier-film-4-x-6-1200-sheets-roll-blackcat-1-bx/</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr"/>
+      <c r="N84" s="5" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr"/>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Blue Barrier Film, 4" x 6", 1200 Sheets</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>My DDS Supply</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>https://myddssupply.com/products/blue-barrier-film-4-x-6-1200-sheets</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="9" t="inlineStr"/>
+      <c r="M85" s="9" t="inlineStr"/>
+      <c r="N85" s="9" t="inlineStr"/>
+      <c r="O85" s="9" t="inlineStr"/>
+      <c r="P85" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film 4" x 6" Blue Roll of 1200 Sheets</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/barrier-film-4-x-6-blue-roll-of-1200-sheets/</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Buy 5 - 9 and pay only $4.85 each, Buy 10 - 14 and pay only $4.75 each, Buy 15 - 19 and pay only $4.65 each, Buy 20 or above and pay only $4.50 each</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O86" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Exact match in all criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>JMU Dental Barrier Film 4"x6" – 1200 Sheets/Roll, Self ...</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>JMU Dental</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N87" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O87" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P87" s="10" t="inlineStr">
+        <is>
+          <t>Different variant (Clear vs Blue), title and scraped_product_name disagree on variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>House Brand 4" X 6" Barrier Film, Blue, Roll Of 1200 Sheets</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/4-x-6-barrier-film-blue-roll-of-1200-sheets</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O88" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Exact match in all criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Vivid ValuWrap (Pearson) | Dental Product</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Pearson Dental Supply</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13161&amp;catid=6378&amp;subcatid=62831&amp;pid=108178</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N89" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O89" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P89" s="10" t="inlineStr">
+        <is>
+          <t>Different variant (Clear vs Blue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Minimal quantity for this product is 1</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Exact match in all criteria, scraped_variant confirms Blue variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Dental City - Barrier Film 4x6 Perforated Sheets</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/17348/dental-city-barrier-film-4x6-perforated-sheets</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M91" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N91" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P91" s="10" t="inlineStr">
+        <is>
+          <t>Exact match in all criteria, scraped_variant confirms Blue variant</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>1469109</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Essentials 4" x 6" Barrier Film, Blue, 1200/Pk</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/essentials-4-x-6-barrier-film-blue-d-188821</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Exact match in all criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal ...</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>Broward A&amp;C Medical Supply</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>118</v>
+      </c>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="9" t="inlineStr"/>
+      <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
+      <c r="O93" s="9" t="inlineStr"/>
+      <c r="P93" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Silhouette SIL2-SM-12 Nitrous Unit Nasal Masks &amp; ...</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/silhouette-sil2-sm-12-nitrous-unit-nasal-masks-breathing-circuit/</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Nitrous Oxide Accessories - Anesthetics</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/nitrous-oxide-accessories-1/</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>128.24</v>
+      </c>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="9" t="inlineStr"/>
+      <c r="M95" s="9" t="inlineStr"/>
+      <c r="N95" s="9" t="inlineStr"/>
+      <c r="O95" s="9" t="inlineStr"/>
+      <c r="P95" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Axess Nasal Mask, Medium, Unscented, 24/bx, Low profile, ...</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>172.25</v>
+      </c>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>178.99</v>
+      </c>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="9" t="inlineStr"/>
+      <c r="M97" s="9" t="inlineStr"/>
+      <c r="N97" s="9" t="inlineStr"/>
+      <c r="O97" s="9" t="inlineStr"/>
+      <c r="P97" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Accutron Multi-Use Nasal Mask, Medium, 1/pk. ...</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/accutron-multiuse-nasal-mask-medium-1-autoclavable-d-148801</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Different brand and product name, also different pack quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Porter Silhouette Nasal Masks</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Sedation Resource</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>https://sedationresource.com/porter-silhouette-nasal-masks/</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="G99" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M99" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N99" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O99" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P99" s="10" t="inlineStr">
+        <is>
+          <t>Different variant (Adult Small instead of Medium)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Silhouette Nitrous Oxide Masks and Breathing Circuits</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Equipment/Small-Equipment/Nitrous-Hoods-%26-Liners/Silhouette%C2%A0Nitrous-Oxide-Masks-and-Breathing-Circuits/p/330832-1</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>96.47</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O100" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Different variant (Mint instead of just Medium), and product name includes additional information</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="G101" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M101" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N101" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P101" s="10" t="inlineStr">
+        <is>
+          <t>Product name includes '-2 Low Profile', which might indicate a different product version</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Porter Silhouette Low Profile Nasal Mask and Breathing ...</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Patterson Dental</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5" t="inlineStr"/>
+      <c r="M102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr"/>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Silhouette Nasal Mask User Manual - Dentserve</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>dentserve.com</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dentserve.com/mwdownloads/download/link/id/9270</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>Order in case of 12 Circuits</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="9" t="inlineStr"/>
+      <c r="M103" s="9" t="inlineStr"/>
+      <c r="N103" s="9" t="inlineStr"/>
+      <c r="O103" s="9" t="inlineStr"/>
+      <c r="P103" s="10" t="inlineStr">
+        <is>
+          <t>price None failed sanity vs Schein unit 120.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>1459489</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Silhouette 2 Low Profile Nasal Masks Medium 12/pack</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Dental Health Products</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5" t="inlineStr"/>
+      <c r="M104" s="5" t="inlineStr"/>
+      <c r="N104" s="5" t="inlineStr"/>
+      <c r="O104" s="5" t="inlineStr"/>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>3cc Luer Lock Disposable Syringes (Non Sterile) (Box of 100)</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3cc-luer-lock-disposable-syringes-non-sterile-box-of-100-plastcare-usa-pg-s3cc</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G105" s="9" t="n"/>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="9" t="inlineStr"/>
+      <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
+      <c r="O105" s="9" t="inlineStr"/>
+      <c r="P105" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Syringe Luer Lock 3cc Low Dead Space Plunger w</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/exel-international-inc-syringe-luer-lock-3cc-low-dead-space-plunger-with-cap/</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr"/>
+      <c r="O106" s="5" t="inlineStr"/>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Exel 3cc Luer Lock Syringe with Needle | 100 Pack</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Medical and Lab Supplies</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="G107" s="9" t="n"/>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr"/>
+      <c r="N107" s="9" t="inlineStr"/>
+      <c r="O107" s="9" t="inlineStr"/>
+      <c r="P107" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Medex Supply</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="inlineStr"/>
+      <c r="M108" s="5" t="inlineStr"/>
+      <c r="N108" s="5" t="inlineStr"/>
+      <c r="O108" s="5" t="inlineStr"/>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>McKesson Safety Hypodermic Syringe 3 mL</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/safety-hypodermic-syringe-with-needle-mckesson-prevent%C2%AE-3-ml-1-1-2-inch-22-gauge-hinged-safety-needle-ultra-thin-wall</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="G109" s="9" t="n"/>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr"/>
+      <c r="O109" s="9" t="inlineStr"/>
+      <c r="P109" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Irrigating Products - Endodontics</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/irrigating-products/</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5" t="inlineStr"/>
+      <c r="M110" s="5" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr"/>
+      <c r="O110" s="5" t="inlineStr"/>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Endo Irrigation Syringes &amp; Half Cut Needles, 3 cc, 27 Ga ...</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/endo-irrigation-syringes-half-cut-needles-3-cc-27-ga-yellow-100-pk-en27h-33071</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G111" s="9" t="n"/>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="9" t="inlineStr"/>
+      <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
+      <c r="O111" s="9" t="inlineStr"/>
+      <c r="P111" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Bound Tree Medical</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5" t="inlineStr"/>
+      <c r="M112" s="5" t="inlineStr"/>
+      <c r="N112" s="5" t="inlineStr"/>
+      <c r="O112" s="5" t="inlineStr"/>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Essentials 12cc Luer Lock Syringe, 100/Pk</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/essentials-12cc-luer-lock-syringe-100-pk-d-188871</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="G113" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="9" t="inlineStr"/>
+      <c r="M113" s="9" t="inlineStr"/>
+      <c r="N113" s="9" t="inlineStr"/>
+      <c r="O113" s="9" t="inlineStr"/>
+      <c r="P113" s="10" t="inlineStr">
+        <is>
+          <t>volume/size mismatch after normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Vista - Luer Lock Syringes - 3cc 100/pack, 316030</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/vista-luer-lock-syringes-3cc-100-pack-137173</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Different brand name (Vista) but same product type</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>Best Selling Products – Page 7</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>My DDS Supply</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>https://myddssupply.com/collections/best-selling-products?page=7</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="9" t="inlineStr"/>
+      <c r="M115" s="9" t="inlineStr"/>
+      <c r="N115" s="9" t="inlineStr"/>
+      <c r="O115" s="9" t="inlineStr"/>
+      <c r="P115" s="10" t="inlineStr">
+        <is>
+          <t>price 91.99 failed sanity vs Schein unit 17.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>RMH3 Dental Luer-Lock Endo Irrigation Syringes, 3cc, 100/ ...</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/rmh3-luerlock-endo-irrigation-syringes-3cc-100-d-168420</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Different product name (RMH3 Dental Luer-Lock Endo Irrigation Syringes) but same product family and specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>5701400</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>3D Dental Luer Lock Syringe 6cc 100/Bx</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/luer-lock-syringe-6cc-100-bx</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="9" t="inlineStr"/>
+      <c r="M117" s="9" t="inlineStr"/>
+      <c r="N117" s="9" t="inlineStr"/>
+      <c r="O117" s="9" t="inlineStr"/>
+      <c r="P117" s="10" t="inlineStr">
+        <is>
+          <t>volume/size mismatch after normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>3M™ Clinpro™ Sealant</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Top Quality Manufacturing, LLC</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr"/>
+      <c r="O118" s="5" t="inlineStr"/>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>3M Clinpro Sealant (Solventum) | Dental Product</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>Pearson Dental Supply</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13311&amp;catid=10955&amp;subcatid=16163&amp;pid=37884</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="G119" s="9" t="n"/>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="9" t="inlineStr"/>
+      <c r="M119" s="9" t="inlineStr"/>
+      <c r="N119" s="9" t="inlineStr"/>
+      <c r="O119" s="9" t="inlineStr"/>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Refill 1.2ml Syringe</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="inlineStr"/>
+      <c r="M120" s="5" t="inlineStr"/>
+      <c r="N120" s="5" t="inlineStr"/>
+      <c r="O120" s="5" t="inlineStr"/>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant - Syringe Tips Refill, Black 10/Pk</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/clinpro-sealant-syringe-tips-refill-black-10-d-49828</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="G121" s="9" t="n"/>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="9" t="inlineStr"/>
+      <c r="M121" s="9" t="inlineStr"/>
+      <c r="N121" s="9" t="inlineStr"/>
+      <c r="O121" s="9" t="inlineStr"/>
+      <c r="P121" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Mixing Well With Cover 4Bx</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/3m-clinpro-sealant-mixing-well-with-cover-12621mw-4-per-box/</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="G122" s="5" t="n"/>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr"/>
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr"/>
+      <c r="O122" s="5" t="inlineStr"/>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Solventum | Create beautiful, healthy smiles while growing your ...</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>DDS Dental Supplies</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/solventum/?page=71</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="G123" s="9" t="n"/>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="9" t="inlineStr"/>
+      <c r="M123" s="9" t="inlineStr"/>
+      <c r="N123" s="9" t="inlineStr"/>
+      <c r="O123" s="9" t="inlineStr"/>
+      <c r="P123" s="10" t="inlineStr">
+        <is>
+          <t>not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>All Products</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Curio.Dental</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>https://curio.dental/collections/all-products</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="5" t="inlineStr"/>
+      <c r="M124" s="5" t="inlineStr"/>
+      <c r="N124" s="5" t="inlineStr"/>
+      <c r="O124" s="5" t="inlineStr"/>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>volume/size mismatch after normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>3M Clinpro Sealant Refill Bottle, 12622, 6 mL ...</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-refill-bottle-12622-6-ml-bottle-1-bottle-pack-3m-12622</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="G125" s="9" t="n"/>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="9" t="inlineStr"/>
+      <c r="M125" s="9" t="inlineStr"/>
+      <c r="N125" s="9" t="inlineStr"/>
+      <c r="O125" s="9" t="inlineStr"/>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant, Refill Syringes, 1.2 ml, 1/Pk</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>https://www.frontierdental.com/us/en/product/clinpro-sealant-refill-syringes-1-2-ml-1-pk-37628</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Exact match with all criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Tri County Dental Supply</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P127" s="10" t="inlineStr">
+        <is>
+          <t>Different variant (with 10 tips) and name mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>3M Clinpro Sealant Refill, Syringe</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Treatments-%26-Prescription-Materials/Sealants/3M-Clinpro-Sealant-Refill%2C-Syringe/p/310009-101</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>1/kit</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Exact match with all criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Amtouch</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>Larger pack (2)</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O129" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P129" s="10" t="inlineStr">
+        <is>
+          <t>Different size/form (bottles) and pack quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Dental Pit and Fissure Sealants</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Dentalcompare.com</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5" t="inlineStr"/>
+      <c r="M130" s="5" t="inlineStr"/>
+      <c r="N130" s="5" t="inlineStr"/>
+      <c r="O130" s="5" t="inlineStr"/>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant - 1.2 ml Syringe Refill with 10 ...</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/clinpro-sealant-12-ml-syringe-refill-10-d-49827</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>Larger pack (10 syringe tips)</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N131" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O131" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>Different pack quantity and includes 10 syringe tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Evacuation System Cleaners - Sky Dental Supply</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/evac-cleaner/</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>BUY 3 GET 1 FREE</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Different brand and product name, also variant 'Sable' does not match</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation System Cleaner</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>Scott's Dental Supply</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scottsdental.com/purevac-sc.html</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="G133" s="9" t="n"/>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="9" t="inlineStr"/>
+      <c r="M133" s="9" t="inlineStr"/>
+      <c r="N133" s="9" t="inlineStr"/>
+      <c r="O133" s="9" t="inlineStr"/>
+      <c r="P133" s="10" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>US Dental Depot</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="n">
+        <v>194.45</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>Exact match in brand, product name, size and pack quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Dentsply Sirona - Purevac SC Evacuation System Cleaner 5L</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/11656/dentsply-sirona-purevac-sc-evacuation-system-cleaner-5l</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>197.73</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>Pack quantity is 5, which is a case</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M135" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N135" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O135" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P135" s="10" t="inlineStr">
+        <is>
+          <t>Different pack quantity, but same product family and size</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Purevac® SC Evacuation System Cleaner - 2 Liter</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Patterson Dental</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="5" t="inlineStr"/>
+      <c r="M136" s="5" t="inlineStr"/>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="5" t="inlineStr"/>
+      <c r="P136" s="6" t="inlineStr">
         <is>
           <t>login required for pricing (public pricing only)</t>
         </is>
@@ -5834,64 +9302,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6001,7 +9526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6050,7 +9575,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
+          <t>https://www.dhpsupply.com/item/120-320062/DHP-Topical-Anesthetic-Gel/</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -6062,12 +9587,12 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2906663</t>
+          <t>5700360</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcompare.com/Restorative-Dentistry/4803-Impression-Material-Mixing-Tips/Compare/?compare=3282424%2C3282425%2C3282426&amp;catid=4803</t>
+          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -6079,12 +9604,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>5703375</t>
+          <t>1126863</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>https://zirc.com/products/denture-box</t>
+          <t>https://shop.benco.com/Product/6094-559/mixing-tips-42-mm-yellow-bag-of-50?Source=Similar.Proton</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -6096,12 +9621,12 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -6113,12 +9638,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
+          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -6130,12 +9655,12 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>https://midwestdental.com/adult-small-silhouette-masks-pk12</t>
+          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -6147,12 +9672,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6164,12 +9689,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
+          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -6181,12 +9706,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>3120099</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/purevac-sc-evac-cleaner-.htm</t>
+          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -6198,15 +9723,66 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-refill-bottle-12622-6-ml-bottle-1-bottle-pack-3m-12622</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>7770371</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>3120099</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>https://www.dhpsupply.com/item/550-21135/PUREVAC-SC-Evacuation-System/</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scottsdental.com/purevac-sc.html</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3120099</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>login required for pricing (public pricing only)</t>
         </is>
@@ -6228,6 +9804,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6257,7 +9836,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parsed Order Audit  ·  tmpvzi7wc3x.pdf</t>
+          <t>Parsed Order Audit  ·  tmpdaqus_dx.pdf</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6630,7 +10209,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Henry Schein</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -6854,7 +10433,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Purevac</t>
+          <t>Dentsply</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">

--- a/output/OR202603121104075460_evidence.xlsx
+++ b/output/OR202603121104075460_evidence.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 20:08</t>
+          <t>Background Evidence  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 23:17</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -655,21 +655,21 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
@@ -711,21 +711,21 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic Gel</t>
+          <t>Gingicaine Strawberry flavored topical anesthetic ...</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
+          <t>https://www.net32.com/ec/gingicaine-strawberry-flavored-topical-anesthetic-benzocaine-20-d-20534</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>6.5</v>
+        <v>8.84</v>
       </c>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="10" t="inlineStr">
@@ -767,21 +767,21 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>ProJel-20, Cherry Flavor, 60 gm Jar. 20% Benzocaine ...</t>
+          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>zoro.com</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/projel20-cherry-flavor-60-gm-jar-20-d-101965</t>
+          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7</v>
+        <v>11.59</v>
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="inlineStr">
@@ -823,21 +823,21 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
+          <t>Gelato Strawberry flavored Topical Anesthetic Gel ...</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>zoro.com</t>
+          <t>The Dental Market U.S.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
+          <t>https://thedentalmarket.net/featured-items/gelato-strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz-jar/</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>11.59</v>
+        <v>11.95</v>
       </c>
       <c r="G7" s="9" t="n"/>
       <c r="H7" s="10" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Opahl Topical Anesthetic Gel 20% Benzocaine</t>
+          <t>Primo Topical Benzocaine Gel 20% - Strawberry, 1oz Jar</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -945,18 +945,18 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/opahl-topical-anesthetic-gel-20-benzocaine-raspberry-d-131159</t>
+          <t>https://www.net32.com/ec/primo-topical-benzocaine-gel-20-strawberry-1oz-d-161921</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>2.97</v>
+        <v>3.99</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 @ $3.99, 6 @ $3.75</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -1009,28 +1009,28 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Topical Anesthetic Gel Strawberry 1oz.</t>
+          <t>House Brand Strawberry Flavored Topical Anesthetic Gel ...</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Davis Dental Supply</t>
+          <t>surgimac.com</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>https://www.davisdentalsupply.com/products/productcode-d332019</t>
+          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2.95</v>
+        <v>3.99</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Re-stocking soon</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>No brand mentioned and different product name</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1083,28 +1083,28 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>House Brand Strawberry Flavored Topical Anesthetic Gel ( ...</t>
+          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>iSmile Dental Products</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
+          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6 for $4.49 each with 10.00% discount</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
@@ -1157,28 +1157,28 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine ...</t>
+          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>iSmile Dental Products</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
+          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>4.99</v>
+        <v>4.5</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Buy 6 for $4.49 each with 10% discount</t>
+          <t>Quantity discounts available</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1257,14 +1257,14 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>Matching brand, product name, size, and pack quantity</t>
+          <t>Title does not include variant, but scraped product name does</t>
         </is>
       </c>
     </row>
@@ -1305,21 +1305,25 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Dental Topical Anesthetic Gel</t>
+          <t>Safco SensiCaine Ultra</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Dental Health Products, Inc.</t>
+          <t>safcodental.com</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/120-320062/DHP-Topical-Anesthetic-Gel/</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
+          <t>https://www.safcodental.com/product/safco-sensicaine-trade-ultra-topical-anesthetic-gel</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -1331,18 +1335,34 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different brand, product name, and variant</t>
         </is>
       </c>
     </row>
@@ -1359,17 +1379,17 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>GEL 1 OZ. BTL STRAWBERRY | PRO-LINE # 018-024</t>
+          <t>20% Benzocaine Gel - Darby Dental</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>darbydental.com</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
+          <t>https://www.darbydental.com/9502997-01.html</t>
         </is>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -1413,21 +1433,21 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Maxima HP High Performance Mixing</t>
+          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
+          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>66.06999999999999</v>
+        <v>234</v>
       </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="6" t="inlineStr">
@@ -1469,7 +1489,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
+          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1479,13 +1499,15 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
+          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>234</v>
-      </c>
-      <c r="G17" s="9" t="n"/>
+        <v>23.86</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>48</v>
+      </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -1493,22 +1515,38 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
-      <c r="N17" s="9" t="inlineStr"/>
-      <c r="O17" s="9" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1525,21 +1563,21 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1: ...</t>
+          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>23.86</v>
+        <v>5.95</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>48</v>
@@ -1555,7 +1593,7 @@
         </is>
       </c>
       <c r="J18" s="5" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>90</v>
@@ -1572,7 +1610,7 @@
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -1582,7 +1620,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Different product variant and size</t>
         </is>
       </c>
     </row>
@@ -1599,40 +1637,40 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
+          <t>Practicon HP Universal Mixing Tips, Yellow 4.2mm, Pack of 48</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>jobs.pfefferwerk.de</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+          <t>https://jobs.pfefferwerk.de/products/practicon-hp-universal-mixing-tips-yellow-42mm-pack-of-48</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>5.95</v>
+        <v>32.99</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>48</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No minimum order required.</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
@@ -1641,12 +1679,12 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O19" s="9" t="inlineStr">
@@ -1656,7 +1694,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>Different product variant and size</t>
+          <t>Different brand, but similar product name and variant</t>
         </is>
       </c>
     </row>
@@ -1699,11 +1737,11 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>80</v>
@@ -1715,7 +1753,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -1730,7 +1768,7 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but same product name and variant</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -1747,21 +1785,21 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>High Performance Mixing Tips Yellow 4.2mm</t>
+          <t>Maxima HP High Performance Mixing</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Pearsonlab.com</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>https://www.pearsonlab.com/catalog/product.asp?majcatid=4547&amp;catid=7084&amp;subcatid=72363&amp;pid=76855&amp;page=1</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/Maxima-HP-High-Performance-Mixing/p/180785-3</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>35.5</v>
+        <v>39.73</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>48</v>
@@ -1777,14 +1815,14 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
@@ -1804,7 +1842,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but same product name and variant</t>
+          <t>Same brand and product name, but variant not explicitly mentioned in title</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1880,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>2-pack price (ordered pack: 48)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1851,10 +1889,10 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
@@ -1878,7 +1916,7 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Different product and pack quantity, title and scraped product name disagree</t>
+          <t>Completely different product</t>
         </is>
       </c>
     </row>
@@ -1916,16 +1954,16 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Larger pack/case</t>
+          <t>Larger pack</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>80</v>
@@ -1937,7 +1975,7 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
@@ -1952,24 +1990,24 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>Different brand and pack quantity, but same product name and variant</t>
+          <t>Different brand and product name, larger pack quantity</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>3250497</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg</t>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Mixing Tips 4.2 mm Yellow Bag of 50</t>
+          <t>Oral-B Glide Healthy Gums Floss 160M Refill Unflavored ...</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1979,10 +2017,12 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6094-559/mixing-tips-42-mm-yellow-bag-of-50?Source=Similar.Proton</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n"/>
+          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>14.29</v>
+      </c>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -1991,7 +2031,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J24" s="5" t="n">
@@ -2006,7 +2046,7 @@
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -2023,64 +2063,46 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Pro-Health Healthy Gums Floss, 160M</t>
+          <t>Oral-B® Glide Healthy Gums Floss with Dispenser 160m</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/oralb-glide-prohealth-healthy-gums-floss-160m-d-184088</t>
+          <t>https://www.practicon.com/glide-pro-health-original-floss-160m-with-dispenser/p/71016231</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>1</v>
-      </c>
+        <v>21.59</v>
+      </c>
+      <c r="G25" s="9" t="n"/>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Smaller pack quantity</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr"/>
+      <c r="N25" s="9" t="inlineStr"/>
+      <c r="O25" s="9" t="inlineStr"/>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>Different product variant (Pro-Health Healthy Gums) and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -2097,25 +2119,23 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss Refill 160m 2/Bx ...</t>
+          <t>Oral-B Glide Healthy Gums Unwaxed Teflon Floss 160 ...</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Dental Wholesale Direct</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+          <t>https://dentalwholesaledirect.com/preventives/oral-b-glide-healthy-gums-unwaxed-teflon-floss-160-meters-ea/</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>21.95</v>
+      </c>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -2123,38 +2143,22 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Exact match with reference product</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -2171,21 +2175,21 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss 160M Refill Unflavored ...</t>
+          <t>Preventives - Floss - DDS Dental Supplies</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
+          <t>https://ddsdentalsupplies.com/floss-5/</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>14.29</v>
+        <v>48.17</v>
       </c>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="10" t="inlineStr">
@@ -2195,7 +2199,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
@@ -2210,7 +2214,7 @@
       <c r="O27" s="9" t="inlineStr"/>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -2227,64 +2231,46 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Oral-B® Glide Healthy Gums Floss with Dispenser 160m</t>
+          <t>Oral-B Superfloss Office Pack Mint 50ct | 80721154 - Supply Clinic</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/glide-pro-health-original-floss-160m-with-dispenser/p/71016231</t>
+          <t>https://www.supplyclinic.com/items/oral-b-superfloss-office-pack-mint-50ct-procter-gamble-80721154</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G28" s="5" t="n"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Smaller pack quantity and includes dispenser</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Different product variant (with dispenser) and pack quantity</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -2301,40 +2287,40 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Unwaxed Teflon Floss 160 ...</t>
+          <t>Glide Floss Picks with Scope, 3 flosser/pk, 72 pk/bx Shred resistant ...</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Dental Wholesale Direct</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>https://dentalwholesaledirect.com/preventives/oral-b-glide-healthy-gums-unwaxed-teflon-floss-160-meters-ea/</t>
+          <t>https://www.supplyclinic.com/items/glide-floss-picks-with-scope-3-flosser-pk-72-pk-bx-shred-resistant-floss-procter-gamble-80754437</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>11.95</v>
+        <v>48.29</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Smaller pack quantity</t>
+          <t>Add $200 for free shipping from Dental District!</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
@@ -2348,7 +2334,7 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O29" s="9" t="inlineStr">
@@ -2358,7 +2344,7 @@
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>Different product variant (unwaxed Teflon) and pack quantity</t>
+          <t>Different product variant and size</t>
         </is>
       </c>
     </row>
@@ -2375,24 +2361,24 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Maxill E-Z Slide max PACK 218 yd Waxed Floss ...</t>
+          <t>Oral-B Glide Pro-Health Dental Floss Original 50 M Value ...</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Tom Thumb</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/ez-slide-max-pack-218-yd-waxed-d-188208</t>
+          <t>https://www.tomthumb.com/shop/product-details.960176476.html</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>4.99</v>
+        <v>14.99</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
@@ -2405,34 +2391,34 @@
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product</t>
+          <t>Different product variant and size</t>
         </is>
       </c>
     </row>
@@ -2449,24 +2435,24 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Preventives - Floss</t>
+          <t>Oral-B Glide Healthy Gums Floss Refill 160m 2/Bx ...</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/floss-5/</t>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>5.69</v>
+        <v>11.25</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
@@ -2475,38 +2461,38 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>95</v>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O31" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
@@ -2523,28 +2509,28 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Intenso Mouthwash - 500ml Anti-Cavity Freshness</t>
+          <t>Glide Pro Health Unwaxed Teflon Floss (Oral-B) - Sky Dental Supply</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/fazzet-intenso-anti-cavity-mouthwash-x-500ml</t>
+          <t>https://www.skydentalsupply.com/oral-b-glide-floss-.htm</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>1-pack price (ordered pack: 2)</t>
+          <t>Single pack</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2553,34 +2539,34 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Completely different product (mouthwash)</t>
+          <t>Different product variant and pack quantity</t>
         </is>
       </c>
     </row>
@@ -2597,21 +2583,25 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss 160m Disp Vial 1/Bx ...</t>
+          <t>https://www.net32.com/ec/oralb-glide-prohealth-hea...</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>D C Dental Supply</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
+          <t>https://www.net32.com/ec/oralb-glide-prohealth-healthy-gums-floss-2-d-184417</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -2619,22 +2609,38 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="9" t="inlineStr"/>
-      <c r="N33" s="9" t="inlineStr"/>
-      <c r="O33" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
@@ -2651,48 +2657,64 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Ivory Toothbrush Cap for Hygiene</t>
+          <t>Oral-B Glide Healthy Gums Floss 160M Refill unflavored, 2 count ...</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>admin.frontierdental.com</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/toothbrush-cap-ivory-438</t>
+          <t>https://admin.frontierdental.com/us/en/product/oral-b-glide-healthy-gums-floss-160m-refill-unflavored-2-count-replaces-proc-80303244-239653</t>
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>123.99</v>
+        <v>14.04</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Free Shipping on $100+ Orders</t>
+          <t>Out of stock</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>price 123.99 failed sanity vs Schein unit 16.62</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
@@ -2709,21 +2731,21 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Glide Healthy Gums Floss 160M Refill unflavored, 2 ...</t>
+          <t>P&amp;G Oral-B Glide Pro-Health Floss Original Font Refills, UnWaxed ...</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>optimusdentalsupply.com</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>https://admin.frontierdental.com/us/en/product/oral-b-glide-healthy-gums-floss-160m-refill-unflavored-2-count-replaces-proc-80303244-239653</t>
+          <t>https://optimusdentalsupply.com/preventives/p-g-oral-b-glide-pro-health-floss-original-font-refills-unwaxed-unflavored-160m-spool-2-bx/</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>14.04</v>
+        <v>13.85</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>2</v>
@@ -2739,10 +2761,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -2766,7 +2788,7 @@
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>Exact match with reference product</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
@@ -2804,19 +2826,19 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>1 @ $267.97,  2 @ $256.98</t>
+          <t>1 unit</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -2840,7 +2862,7 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Different flavor (Watermelon vs No Flavor)</t>
+          <t>Different flavor (Watermelon) than the reference product (No Flavor)</t>
         </is>
       </c>
     </row>
@@ -2857,64 +2879,64 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>LOCATOR Replacement Denture Cap Male Assembly, 10/Pk</t>
+          <t>Clinpro™ In Office 2.1% NaF Clear Fluoride Treatment</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Top Quality Manufacturing, LLC</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/locator-replacement-denture-cap-male-assembly-10-d-178963</t>
+          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>182.99</v>
+        <v>142.49</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size (50) than the reference product (100)</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O37" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>Completely different product</t>
+          <t>Different flavor (Mint) and pack quantity than the reference product</t>
         </is>
       </c>
     </row>
@@ -2931,46 +2953,64 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Clinpro™ In Office 2.1% NaF Clear Fluoride Treatment</t>
+          <t>3M - Clinpro Clear Fluoride Varnish 100/Pack</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Top Quality Manufacturing, LLC</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
+          <t>https://www.dentalcity.com/product/21837/3m-clinpro-clear-fluoride-varnish-100pack</t>
         </is>
       </c>
       <c r="F38" s="8" t="n">
-        <v>285.99</v>
-      </c>
-      <c r="G38" s="5" t="n"/>
+        <v>294.99</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4, Get 1 Free</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr"/>
-      <c r="O38" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>Different flavor (Mint) than the reference product (No Flavor)</t>
         </is>
       </c>
     </row>
@@ -2987,28 +3027,28 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>3M - Clinpro Clear Fluoride Varnish 100/Pack</t>
+          <t>3M Clinpro Clear Fluoride Treatment</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/21837/3m-clinpro-clear-fluoride-varnish-100pack</t>
+          <t>https://www.scottsdental.com/3m-clinpro-clear-fluoride-treatment.html</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>294.99</v>
+        <v>133.95</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Buy 4, Get 1 Free</t>
+          <t>Smaller pack size (50) than the reference product (100)</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -3017,10 +3057,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
@@ -3039,12 +3079,12 @@
       </c>
       <c r="O39" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>Different flavor (Mint vs No Flavor)</t>
+          <t>Different flavor (Mint) and pack quantity than the reference product</t>
         </is>
       </c>
     </row>
@@ -3066,23 +3106,23 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>Safco Dental Supply</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/3m-clinpro-clear-fluoride-treatment.html</t>
+          <t>https://www.safcodental.com/product/3m-sup-trade-sup-clinpro-sup-trade-sup-clear-fluoride-treatment</t>
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>133.95</v>
+        <v>272.99</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>Buy 4, Get 1 FREE!</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3091,7 +3131,7 @@
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>80</v>
@@ -3113,12 +3153,12 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Different pack quantity (50 vs 100) and flavor (Mint vs No Flavor)</t>
+          <t>Different flavor (mint) than the reference product (No Flavor)</t>
         </is>
       </c>
     </row>
@@ -3135,94 +3175,76 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Treatment</t>
+          <t>3M™ Clinpro™ Clear Fluoride Treatment Mint Flavor 0.5 ...</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Safco Dental Supply</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/3m-sup-trade-sup-clinpro-sup-trade-sup-clear-fluoride-treatment</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>272.99</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>100</v>
-      </c>
+          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>No minimum order condition listed.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N41" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O41" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L41" s="9" t="inlineStr"/>
+      <c r="M41" s="9" t="inlineStr"/>
+      <c r="N41" s="9" t="inlineStr"/>
+      <c r="O41" s="9" t="inlineStr"/>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>Different flavor (Mint vs No Flavor)</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>5703169</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk</t>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>3M™ Clinpro™ Clear Fluoride Treatment Mint Flavor 0.5 ...</t>
+          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Benco Dental</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n"/>
+          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>153.9</v>
+      </c>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
@@ -3231,7 +3253,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J42" s="5" t="n">
@@ -3246,7 +3268,7 @@
       <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3285,12 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>2pro Total Access Prophy Angle with Soft/Short Purple Cup ...</t>
+          <t>2pro Total Access Prophy Angle with Soft/Short Purple Cup ... - Net32</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -3319,12 +3341,12 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>MARK3 Disposable Prophy Angle with SOFT GREEN CUP</t>
+          <t>MARK3 Disposable Prophy Angle with SOFT GREEN CUP, 500/Bx</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -3375,25 +3397,23 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
+          <t>Prophy Angles</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
+          <t>https://www.practicon.com/exam-hygiene/prophylaxis/prophy-angles/</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>355.09</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>500</v>
-      </c>
+        <v>236.99</v>
+      </c>
+      <c r="G45" s="9" t="n"/>
       <c r="H45" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -3401,38 +3421,22 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N45" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O45" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="inlineStr"/>
+      <c r="M45" s="9" t="inlineStr"/>
+      <c r="N45" s="9" t="inlineStr"/>
+      <c r="O45" s="9" t="inlineStr"/>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -3449,40 +3453,40 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Safco CleanCare disposable prophy angles</t>
+          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Safco Dental Supply</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
+          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>26.99</v>
+        <v>355.09</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J46" s="5" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
@@ -3491,22 +3495,22 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Different brand and pack quantity</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -3523,40 +3527,40 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
+          <t>Safco CleanCare disposable prophy angles</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Safco Dental Supply</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
+          <t>https://www.safcodental.com/product/safco-cleancare-trade-disposable-prophy-angles</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>263.85</v>
+        <v>26.99</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
@@ -3565,22 +3569,22 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O47" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>Different brand, but similar product name and description</t>
         </is>
       </c>
     </row>
@@ -3597,64 +3601,64 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Perfect Choice Prophy Angles Soft Gray 500/Box</t>
+          <t>ACCLEAN by Henry Schein | Prophy Angles</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Perfect-Choice-Prophy-Angles-514650</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
         </is>
       </c>
       <c r="F48" s="8" t="n">
-        <v>153.9</v>
+        <v>71.86</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Quantity discounts available</t>
+          <t>Smaller pack size</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Different brand, but similar product name</t>
+          <t>Different product name and description</t>
         </is>
       </c>
     </row>
@@ -3671,28 +3675,28 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>ACCLEAN by Henry Schein | Prophy Angles</t>
+          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
+          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>71.86</v>
+        <v>263.85</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Smaller pack size</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -3701,14 +3705,14 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M49" s="9" t="inlineStr">
@@ -3723,12 +3727,12 @@
       </c>
       <c r="O49" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>Different product name and pack quantity</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,9 @@
         </is>
       </c>
       <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -3799,40 +3805,40 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Perfect Choice Soft Prophy Angles Bulk 500/Box</t>
+          <t>Dream Disposable Prophy Angle, Latex Free, Soft, 100/Pk, DPA100S</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>frontierdental.com</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/perfect-choice-soft-prophy-angles-bulk-500-box/p/702938</t>
+          <t>https://frontierdental.com/us/en/product/dream-disposable-prophy-angle-latex-free-soft-100-pk-dpa100s-33009</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>177.29</v>
+        <v>42.99</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>500</v>
+        <v>64</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>No minimum order condition specified</t>
+          <t>Different product</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
@@ -3841,22 +3847,22 @@
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N51" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O51" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>Different brand, but similar product name</t>
+          <t>Completely different product</t>
         </is>
       </c>
     </row>
@@ -3873,21 +3879,21 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Ultra Smartmix - B1, 15 Gm. Syringe and 10 ...</t>
+          <t>DMG Products - Dental Wholesale Direct</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>dentalwholesaledirect.com</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/luxatemp-ultra-smartmix-b1-15-gm-syringe-d-115709</t>
+          <t>https://dentalwholesaledirect.com/dmg/</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>64.89</v>
+        <v>62.95</v>
       </c>
       <c r="G52" s="5" t="n"/>
       <c r="H52" s="6" t="inlineStr">
@@ -3985,21 +3991,21 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Crown &amp; Bridge - Temporary Material</t>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/temporary-material/</t>
+          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
         </is>
       </c>
       <c r="F54" s="8" t="n">
-        <v>96.34</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="6" t="inlineStr">
@@ -4041,21 +4047,21 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Plus</t>
+          <t>Crown &amp; Bridge - Temporary Material - DDS Dental Supplies</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Scott's Dental Supply</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
+          <t>https://ddsdentalsupplies.com/temporary-material/</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>449.95</v>
+        <v>96.34</v>
       </c>
       <c r="G55" s="9" t="n"/>
       <c r="H55" s="10" t="inlineStr">
@@ -4097,25 +4103,23 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Intra Oral Mixing Tips for Brown Tips 25 pcs/pk</t>
+          <t>LUXATEMP PLUS FINE MIX TIPS (25/PK)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Anson Dental Supply</t>
+          <t>Newark Dental-Pemco</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>https://ansondental.com/products/intra-oral-mixing-tips-for-brown-tips-25-pcs-pk</t>
+          <t>https://newarkdentalpemco.com/products/luxatemp-plus-fine-mix-tips</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>25</v>
-      </c>
+        <v>396.98</v>
+      </c>
+      <c r="G56" s="5" t="n"/>
       <c r="H56" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -4123,38 +4127,22 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr"/>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -4171,64 +4159,46 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Manufacturer Promotions | Save on Dental Brands</t>
+          <t>Luxatemp Plus</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>https://www.frontierdental.com/ca/en/manufacturer-promotions?banner_promo=eyJpdiI6Ik5LVm10bDdYcnpCb3F6TFRCVmJoZlE9PSIsInZhbHVlIjoieWFVbWZoWlY0NnROYzlSMGFCWkpVQT09IiwibWFjIjoiNWVhYmZmNzRkZmFhZGFiNGRlOGI2MDI0YmVkYzFmODBjMzVhNGNmYzU0MTZhZTY4Yjg1N2FhYzE2NzY3OWRiMSIsInRhZyI6IiJ9&amp;page=54</t>
+          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="G57" s="9" t="n">
-        <v>500</v>
-      </c>
+        <v>449.95</v>
+      </c>
+      <c r="G57" s="9" t="n"/>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Larger pack/case</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M57" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O57" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr"/>
+      <c r="O57" s="9" t="inlineStr"/>
       <c r="P57" s="10" t="inlineStr">
         <is>
-          <t>Completely different product</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -4245,28 +4215,28 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer Promotions | Save on Dental Brands</t>
+          <t>Intra Oral Mixing Tips for Brown Tips 25 pcs/pk</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>Anson Dental Supply</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>https://www.frontierdental.com/ca/en/manufacturer-promotions?banner_promo=eyJpdiI6Ik5LVm10bDdYcnpCb3F6TFRCVmJoZlE9PSIsInZhbHVlIjoieWFVbWZoWlY0NnROYzlSMGFCWkpVQT09IiwibWFjIjoiNWVhYmZmNzRkZmFhZGFiNGRlOGI2MDI0YmVkYzFmODBjMzVhNGNmYzU0MTZhZTY4Yjg1N2FhYzE2NzY3OWRiMSIsInRhZyI6IiJ9&amp;page=14</t>
+          <t>https://ansondental.com/products/intra-oral-mixing-tips-for-brown-tips-25-pcs-pk</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>20.99</v>
+        <v>4.99</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Larger pack/case</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -4275,10 +4245,10 @@
         </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
@@ -4292,17 +4262,17 @@
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Completely different product</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
@@ -4319,28 +4289,28 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Dental Mixing Tips HP Blue-Orange - Pack Of 49 Disposable ...</t>
+          <t>Mixing Tips - Dental Supplies - TDSC.com</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>oktowallz.com</t>
+          <t>tdsc.com</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>https://oktowallz.com/view/Orange-Pack-Of-49-Disposable-Tips-For-Dental-Impression/833810</t>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Dispensing-%26-Mixing-Products/Dispensing-Products/Mixing-Tips/c/539</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>13.99</v>
+        <v>33.99</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
@@ -4349,10 +4319,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
@@ -4366,17 +4336,17 @@
       </c>
       <c r="N59" s="9" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O59" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="P59" s="10" t="inlineStr">
         <is>
-          <t>Different product and pack quantity</t>
+          <t>Different brand, product name, and pack quantity</t>
         </is>
       </c>
     </row>
@@ -4423,10 +4393,10 @@
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
@@ -4488,7 +4458,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>No Returns</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
@@ -4541,24 +4511,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
+          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Patterson Dental</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>58.27</v>
-      </c>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n"/>
       <c r="G62" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
@@ -4567,38 +4535,22 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr"/>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Light Blue instead of Fine), but same product family</t>
+          <t>price None failed sanity vs Schein unit 82.19</t>
         </is>
       </c>
     </row>
@@ -4615,21 +4567,25 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Luxatemp Automix Plus Tips – Fine, 25/Bag</t>
+          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Patterson Dental</t>
+          <t>MVP Dental Supply</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/073241510</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
+          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -4637,22 +4593,38 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr"/>
-      <c r="N63" s="9" t="inlineStr"/>
-      <c r="O63" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P63" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 82.19</t>
+          <t>Marketing-name variation of the same product line</t>
         </is>
       </c>
     </row>
@@ -4669,25 +4641,21 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>DMG 110351 Luxatemp Plus Automix Dental Mixing Tips ...</t>
+          <t>Luxatemp Automix Plus Shade A2 Refill Kit - Benco Dental</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>MVP Dental Supply</t>
+          <t>shop.benco.com</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>https://mvpdentalsupply.com/products/dmg-america-110351-luxatemp-plus-mixing-tips-fine-pk-25</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="n">
-        <v>75.04000000000001</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>25</v>
-      </c>
+          <t>https://shop.benco.com/Product/2420-006/luxatemp-automix-plus-shade-a2-refill-kit</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
       <c r="H64" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -4695,38 +4663,22 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr"/>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Marketing-name variation of the same product line</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -4743,21 +4695,21 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Denture Storage Boxes 12/Pk Red</t>
+          <t>Assorted Denture Box Pack of 12 | Benco Dental</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>shop.benco.com</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Denture-Storage-Boxes-9576660</t>
+          <t>https://shop.benco.com/Product/4543-835/assorted-denture-box-pack-of-12</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>15.65</v>
+        <v>11.79</v>
       </c>
       <c r="G65" s="9" t="n"/>
       <c r="H65" s="10" t="inlineStr">
@@ -4799,21 +4751,21 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Denture Box - 12 Pack</t>
+          <t>Denture Storage Boxes</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Zirc Dental Products</t>
+          <t>Keystone Industries</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>https://zirc.com/products/denture-box</t>
+          <t>https://dental.keystoneindustries.com/product/denture-storage-boxes/</t>
         </is>
       </c>
       <c r="F66" s="8" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G66" s="5" t="n"/>
       <c r="H66" s="6" t="inlineStr">
@@ -4855,21 +4807,21 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Oral-B Indicator Toothbrush 35 Soft Assorted Colors 12Bx</t>
+          <t>Denture Boxes 12/Pk Assorted | Guaranteed Lowest Price</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/indicator-toothbrush-35-soft/</t>
+          <t>https://www.crazydentalprices.com/Denture-Boxes-30R800_2</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>19.67</v>
+        <v>15.6</v>
       </c>
       <c r="G67" s="9" t="n"/>
       <c r="H67" s="10" t="inlineStr">
@@ -4911,21 +4863,21 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>New Age Denture Cases 12/Box</t>
+          <t>Denture Storage Boxes 12/Pk Red</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Practicon, Inc.</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>https://www.practicon.com/new-age-denture-cases-12-box/p/7017057</t>
+          <t>https://www.crazydentalprices.com/Denture-Storage-Boxes-9576660</t>
         </is>
       </c>
       <c r="F68" s="8" t="n">
-        <v>23.99</v>
+        <v>15.65</v>
       </c>
       <c r="G68" s="5" t="n"/>
       <c r="H68" s="6" t="inlineStr">
@@ -4967,21 +4919,21 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Colorful Retainer Boxes - 12 Pack</t>
+          <t>Denture Box - 12 Pack</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>Zirc Dental Products</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/retainer-boxes-assorted-colors-1430</t>
+          <t>https://zirc.com/products/denture-box</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>66.98999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="G69" s="9" t="n"/>
       <c r="H69" s="10" t="inlineStr">
@@ -5023,20 +4975,22 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Dental City - Denture Boxes 12/Pack</t>
+          <t>New Age Denture Cases 12/Box</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Practicon, Inc.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>https://dentalcity.com/product/9911/dental-city-denture-boxes-12pack</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="n"/>
+          <t>https://www.practicon.com/new-age-denture-cases-12-box/p/7017057</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>23.99</v>
+      </c>
       <c r="G70" s="5" t="n"/>
       <c r="H70" s="6" t="inlineStr">
         <is>
@@ -5060,7 +5014,7 @@
       <c r="O70" s="5" t="inlineStr"/>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -5077,64 +5031,46 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Denture Storage Boxes, Assorted, 12/Pk, 100010</t>
+          <t>Essentials Denture Box, Assorted Colors, 12/Pk</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>https://www.frontierdental.com/us/en/product/denture-storage-boxes-assorted-12pk-100010-161115</t>
+          <t>https://www.net32.com/ec/essentials-denture-box-assorted-colors-12-pk-d-188852</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>12</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G71" s="9" t="n"/>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>This item requires special handling - a small fee will be applied once per order during checkout.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M71" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N71" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O71" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr"/>
+      <c r="O71" s="9" t="inlineStr"/>
       <c r="P71" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -5151,38 +5087,40 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>House Brand Denture Boxes, Assorted, Box of 10</t>
+          <t>ProBath Denture Box Assorted 12/Pack 200PBH-PA - Supply Clinic</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>/goto?url=CAESfwHuR6pNuLf0ElkSzuN5KPyNdhRISnExGL4KeUs5o-XYTKiprtrKYZIChSanekD2mxaVMqZz0dK4mcw6FJRK0Q4krLgB5jlEMXb5x_nMw4ZjZVe4WoIqMHaMc_I-jMlL0-rPUsglz362z423suwkgxUFjS_wGp0d3jmBD1J6ys4%3D</t>
+          <t>https://www.supplyclinic.com/items/probath-denture-box-assorted-12-pack-200pbh-pa-plasdent-200pbh-pa</t>
         </is>
       </c>
       <c r="F72" s="8" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="G72" s="5" t="n"/>
+        <v>8.99</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Add $10 for free shipping!</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J72" s="5" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
@@ -5196,17 +5134,17 @@
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Insufficient data</t>
+          <t>Different brand name (ProBath) but same product type</t>
         </is>
       </c>
     </row>
@@ -5223,40 +5161,40 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes, Assorted, 12/bx</t>
+          <t>Assorted 40 Pack Bulk Denture Case Bath Holders Retainers Teeth ...</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Pricenex</t>
+          <t>supplyclinic.com</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
+          <t>https://www.supplyclinic.com/items/assorted-40-pack-bulk-denture-case-bath-holders-retainers-teeth-guards-individually-sealed-plastcare-usa-dent-assr-40</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>5.99</v>
+        <v>39.99</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Larger pack/case</t>
         </is>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
@@ -5265,7 +5203,7 @@
       </c>
       <c r="M73" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N73" s="9" t="inlineStr">
@@ -5275,12 +5213,12 @@
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different pack quantity and variant</t>
         </is>
       </c>
     </row>
@@ -5297,21 +5235,21 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Preventives</t>
+          <t>Ortho Denture &amp; Retainer Boxes - Sky Dental Supply</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/preventives/</t>
+          <t>https://www.skydentalsupply.com/denture-retainer-boxes/</t>
         </is>
       </c>
       <c r="F74" s="8" t="n">
-        <v>7.59</v>
+        <v>7.99</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>12</v>
@@ -5323,38 +5261,38 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Different product</t>
+          <t>Different variant (Primary Color) and brand name (Plasdent)</t>
         </is>
       </c>
     </row>
@@ -5371,23 +5309,25 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Essentials Denture Box, Assorted Colors, 12/Pk</t>
+          <t>Denture Boxes, Assorted, 12/bx</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Pricenex</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>/goto?url=CAEShgEB7keqTYn8uUG8xfuZABXpIutatBQy3XaV36kpcgpmvQnQrGWoVSHwCUAPjmw8nRHGqhY_9iKU-2beQbgV1DvxyVQCIgFLtdzpOrfXBiJSnwoEs5OO88Pkx7YXJJx_e0kIHzAHMue35lsMbfQ1tPoYRICGp36P9oeKLjHbdP3AHZSl0mLTbQ%3D%3D</t>
+          <t>https://pricenex.com/denture-boxes-assorted-12-bx/</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="G75" s="9" t="n"/>
+        <v>5.99</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -5395,38 +5335,38 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N75" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
         <is>
-          <t>Insufficient data</t>
+          <t>Same product name, variant, and pack quantity</t>
         </is>
       </c>
     </row>
@@ -5443,21 +5383,21 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Denture Boxes 12/Pk Assorted | Guaranteed Lowest Price</t>
+          <t>Denture Boxes 12/Pack</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Denture-Boxes-30R800_2</t>
+          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
         </is>
       </c>
       <c r="F76" s="8" t="n">
-        <v>15.4</v>
+        <v>11.17</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>12</v>
@@ -5469,14 +5409,14 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
@@ -5500,7 +5440,7 @@
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Same product name and pack quantity, but different site title</t>
         </is>
       </c>
     </row>
@@ -5517,40 +5457,40 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Denture Boxes 12/Pack</t>
+          <t>PLASDENT # 200BTH-XA - DENTURE BOXES</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/9911/dental-city-denture-boxes</t>
+          <t>https://usdentaldepot.com/plasdent-denture-box-assorted-chr-plasdent-200bth-xa</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>11.17</v>
+        <v>8.18</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
@@ -5559,7 +5499,7 @@
       </c>
       <c r="M77" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N77" s="9" t="inlineStr">
@@ -5574,7 +5514,7 @@
       </c>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Different variant (Chroma Colored) and brand name (PLASDENT)</t>
         </is>
       </c>
     </row>
@@ -5591,64 +5531,44 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>PLASDENT # 200BTH-XA - DENTURE BOXES</t>
+          <t>Assorted Colors Denture Box Pack of 12 - Benco Dental</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>US Dental Depot</t>
+          <t>shop.benco.com</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>https://usdentaldepot.com/plasdent-denture-box-assorted-chr-plasdent-200bth-xa</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>12</v>
-      </c>
+          <t>https://shop.benco.com/Product/1707-860/assorted-colors-denture-box-pack-of-12</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N78" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O78" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="5" t="inlineStr"/>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -5665,21 +5585,21 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Dukal Unipack Barrier Film - Infection Control</t>
+          <t>Cover Film - Orthazone</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Optimus Dental Supply</t>
+          <t>orthazone.com</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>https://optimusdentalsupply.com/dukal-unipack-barrier-film/</t>
+          <t>https://www.orthazone.com/infection-control-sterilization/dental-surface-cleaners/cover-film-infection-control</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>8.449999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="G79" s="9" t="n"/>
       <c r="H79" s="10" t="inlineStr">
@@ -5721,21 +5641,21 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>2026 Spring Savings</t>
+          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Pearson Dental Supply</t>
+          <t>Dental Mates</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>https://www.pearsondental.com/savings.asp</t>
+          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
         </is>
       </c>
       <c r="F80" s="8" t="n">
-        <v>10.95</v>
+        <v>12.99</v>
       </c>
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="6" t="inlineStr">
@@ -5777,21 +5697,21 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
+          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Darkside Tattoo Supply Inc</t>
+          <t>Cam Supply</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
+          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>12.88</v>
+        <v>15</v>
       </c>
       <c r="G81" s="9" t="n"/>
       <c r="H81" s="10" t="inlineStr">
@@ -5833,21 +5753,21 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Dental Barrier Film Sticky Wrap in Blue 4" x 6" (1200 Sheet)</t>
+          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Dental Mates</t>
+          <t>Darkside Tattoo Supply Inc</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>https://dentalmates.com/products/dental-barrier-film-sticky-wrap-in-blue-4-x-6-1200-sheet</t>
+          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
         </is>
       </c>
       <c r="F82" s="8" t="n">
-        <v>12.99</v>
+        <v>15.25</v>
       </c>
       <c r="G82" s="5" t="n"/>
       <c r="H82" s="6" t="inlineStr">
@@ -5889,21 +5809,21 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
+          <t>Sticky Wrap Barrier Film, Colored (Plasdent) | Dental Product ...</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Cam Supply</t>
+          <t>pearsondental.com</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13161&amp;catid=6378&amp;subcatid=82965&amp;pid=59248</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>15</v>
+        <v>17.1</v>
       </c>
       <c r="G83" s="9" t="n"/>
       <c r="H83" s="10" t="inlineStr">
@@ -5945,21 +5865,21 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Dukal Unipack Barrier Film UBC-8045</t>
+          <t>Cover-It Barrier Film 4"x6" 1200/Roll Clear - Crazy Dental</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Optimus Dental Supply</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>https://optimusdentalsupply.com/dukal-unipack-barrier-film-4-x-6-1200-sheets-roll-blackcat-1-bx/</t>
+          <t>https://www.crazydentalprices.com/COVER-IT-Barrier-Film-C101</t>
         </is>
       </c>
       <c r="F84" s="8" t="n">
-        <v>16.05</v>
+        <v>18.69</v>
       </c>
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="6" t="inlineStr">
@@ -6001,21 +5921,21 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Blue Barrier Film, 4" x 6", 1200 Sheets</t>
+          <t>Benco Dental™ Barrier Film Latex Free Blue 4x6" Roll of 1200 Sheets</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>My DDS Supply</t>
+          <t>shop.benco.com</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>https://myddssupply.com/products/blue-barrier-film-4-x-6-1200-sheets</t>
+          <t>https://shop.benco.com/Product/5076-802/benco-dental-barrier-film-latex-free-blue-4x6-roll</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>19.99</v>
+        <v>29.79</v>
       </c>
       <c r="G85" s="9" t="n"/>
       <c r="H85" s="10" t="inlineStr">
@@ -6078,7 +5998,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Buy 5 - 9 and pay only $4.85 each, Buy 10 - 14 and pay only $4.75 each, Buy 15 - 19 and pay only $4.65 each, Buy 20 or above and pay only $4.50 each</t>
+          <t>Buy 5 - 9 and pay only $4.85 each; Buy 10 - 14 and pay only $4.75 each; Buy 15 - 19 and pay only $4.65 each; Buy 20 or above and pay only $4.50 each</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -6114,7 +6034,7 @@
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
-          <t>Exact match in all criteria</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6108,7 @@
       </c>
       <c r="P87" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Clear vs Blue), title and scraped_product_name disagree on variant</t>
+          <t>Variant mismatch: Blue vs Clear</t>
         </is>
       </c>
     </row>
@@ -6205,21 +6125,21 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>House Brand 4" X 6" Barrier Film, Blue, Roll Of 1200 Sheets</t>
+          <t>Barrier Film Roll 4" x 6" 1200/Rl - Curio Dental – Curio.Dental</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>curio.dental</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/4-x-6-barrier-film-blue-roll-of-1200-sheets</t>
+          <t>https://curio.dental/products/barrier-film-roll-4-x-6-1200-rl</t>
         </is>
       </c>
       <c r="F88" s="8" t="n">
-        <v>7.99</v>
+        <v>13.97</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>1200</v>
@@ -6231,14 +6151,14 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J88" s="5" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
@@ -6247,7 +6167,7 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
@@ -6262,7 +6182,7 @@
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
-          <t>Exact match in all criteria</t>
+          <t>Variant mismatch: Blue vs Clear</t>
         </is>
       </c>
     </row>
@@ -6279,40 +6199,40 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Vivid ValuWrap (Pearson) | Dental Product</t>
+          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Pearson Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13161&amp;catid=6378&amp;subcatid=62831&amp;pid=108178</t>
+          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>10.95</v>
+        <v>11.99</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>1200</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
@@ -6321,7 +6241,7 @@
       </c>
       <c r="M89" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N89" s="9" t="inlineStr">
@@ -6336,7 +6256,7 @@
       </c>
       <c r="P89" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Clear vs Blue)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6353,28 +6273,28 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Barrier Film 4" x 6" 1200 Perforated Sheets/Roll</t>
+          <t>Dental City - Barrier Film 4x6 Perforated Sheets</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>skydentalsupply.com</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/100z-barrier-film.htm</t>
+          <t>https://www.dentalcity.com/product/17348/dental-city-barrier-film-4x6-perforated-sheets</t>
         </is>
       </c>
       <c r="F90" s="8" t="n">
-        <v>11.99</v>
+        <v>16.49</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>1200</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>Minimal quantity for this product is 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -6410,7 +6330,7 @@
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
-          <t>Exact match in all criteria, scraped_variant confirms Blue variant</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6427,28 +6347,28 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Dental City - Barrier Film 4x6 Perforated Sheets</t>
+          <t>Essentials 4" x 6" Barrier Film, Blue, 1200/Pk</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Dental City</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentalcity.com/product/17348/dental-city-barrier-film-4x6-perforated-sheets</t>
+          <t>https://www.net32.com/ec/essentials-4-x-6-barrier-film-blue-d-188821</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>16.49</v>
+        <v>15.46</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>1200</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 @ $15.46, 3 @ $14.46</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
@@ -6484,7 +6404,7 @@
       </c>
       <c r="P91" s="10" t="inlineStr">
         <is>
-          <t>Exact match in all criteria, scraped_variant confirms Blue variant</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6501,28 +6421,28 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Essentials 4" x 6" Barrier Film, Blue, 1200/Pk</t>
+          <t>Defend Barrier Film Blue 4" x 6" 1200/Roll w/ Dispenser Box ...</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/essentials-4-x-6-barrier-film-blue-d-188821</t>
+          <t>https://www.crazydentalprices.com/Defend-Barrier-Film-BF2500</t>
         </is>
       </c>
       <c r="F92" s="8" t="n">
-        <v>15.46</v>
+        <v>31</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>1200</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>with dispenser box</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -6558,7 +6478,7 @@
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
-          <t>Exact match in all criteria</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6575,21 +6495,21 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal ...</t>
+          <t>Silhouette SIL2-SM-12 Nitrous Unit Nasal Masks &amp; Breathing Circuit</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Broward A&amp;C Medical Supply</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
+          <t>https://ddsdentalsupplies.com/silhouette-sil2-sm-12-nitrous-unit-nasal-masks-breathing-circuit/</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>118</v>
+        <v>128.24</v>
       </c>
       <c r="G93" s="9" t="n"/>
       <c r="H93" s="10" t="inlineStr">
@@ -6631,17 +6551,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Silhouette SIL2-SM-12 Nitrous Unit Nasal Masks &amp; ...</t>
+          <t>Nitrous Oxide Accessories - Anesthetics - DDS Dental Supplies</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/silhouette-sil2-sm-12-nitrous-unit-nasal-masks-breathing-circuit/</t>
+          <t>https://ddsdentalsupplies.com/nitrous-oxide-accessories-1/</t>
         </is>
       </c>
       <c r="F94" s="8" t="n">
@@ -6687,21 +6607,21 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Nitrous Oxide Accessories - Anesthetics</t>
+          <t>Axess Nasal Mask, Medium, Unscented, 24/bx, Low profile, ...</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Net32</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/nitrous-oxide-accessories-1/</t>
+          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>128.24</v>
+        <v>172.25</v>
       </c>
       <c r="G95" s="9" t="n"/>
       <c r="H95" s="10" t="inlineStr">
@@ -6743,21 +6663,21 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Axess Nasal Mask, Medium, Unscented, 24/bx, Low profile, ...</t>
+          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Supply Clinic</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
         </is>
       </c>
       <c r="F96" s="8" t="n">
-        <v>172.25</v>
+        <v>178.99</v>
       </c>
       <c r="G96" s="5" t="n"/>
       <c r="H96" s="6" t="inlineStr">
@@ -6799,46 +6719,64 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
+          <t>Porter SIL2-MED-12 Silhouette 2 Low Profile Nasal Hood ...</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>frischsnwo.com</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+          <t>https://frischsnwo.com/listing/porter-sil2-med-12-silhouette-2-low-profile-nasal-hood-masks</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>178.99</v>
-      </c>
-      <c r="G97" s="9" t="n"/>
+        <v>44.62</v>
+      </c>
+      <c r="G97" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>single unit</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="9" t="inlineStr"/>
-      <c r="M97" s="9" t="inlineStr"/>
-      <c r="N97" s="9" t="inlineStr"/>
-      <c r="O97" s="9" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M97" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P97" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>different product name and pack quantity</t>
         </is>
       </c>
     </row>
@@ -6855,24 +6793,24 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Accutron Multi-Use Nasal Mask, Medium, 1/pk. ...</t>
+          <t>Porter Silhouette Nasal Masks</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Sedation Resource</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/accutron-multiuse-nasal-mask-medium-1-autoclavable-d-148801</t>
+          <t>https://sedationresource.com/porter-silhouette-nasal-masks/</t>
         </is>
       </c>
       <c r="F98" s="8" t="n">
-        <v>141.21</v>
+        <v>157</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
@@ -6885,34 +6823,34 @@
         </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N98" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O98" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P98" s="6" t="inlineStr">
         <is>
-          <t>Different brand and product name, also different pack quantity</t>
+          <t>different variant (pediatric instead of medium)</t>
         </is>
       </c>
     </row>
@@ -6929,28 +6867,28 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Porter Silhouette Nasal Masks</t>
+          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Sedation Resource</t>
+          <t>Crazy Dental Price Club</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>https://sedationresource.com/porter-silhouette-nasal-masks/</t>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No minimum order required</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
@@ -6959,14 +6897,14 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M99" s="9" t="inlineStr">
@@ -6986,7 +6924,7 @@
       </c>
       <c r="P99" s="10" t="inlineStr">
         <is>
-          <t>Different variant (Adult Small instead of Medium)</t>
+          <t>missing brand name, but same product family</t>
         </is>
       </c>
     </row>
@@ -7003,21 +6941,21 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Silhouette Nitrous Oxide Masks and Breathing Circuits</t>
+          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal ...</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>The Dentists Supply Company</t>
+          <t>Broward A&amp;C Medical Supply</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Equipment/Small-Equipment/Nitrous-Hoods-%26-Liners/Silhouette%C2%A0Nitrous-Oxide-Masks-and-Breathing-Circuits/p/330832-1</t>
+          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
         </is>
       </c>
       <c r="F100" s="8" t="n">
-        <v>96.47</v>
+        <v>118</v>
       </c>
       <c r="G100" s="5" t="n">
         <v>12</v>
@@ -7033,10 +6971,10 @@
         </is>
       </c>
       <c r="J100" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
@@ -7060,7 +6998,7 @@
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
-          <t>Different variant (Mint instead of just Medium), and product name includes additional information</t>
+          <t>marketing name variation, same product line</t>
         </is>
       </c>
     </row>
@@ -7077,25 +7015,21 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
+          <t>Porter Silhouette Low Profile Nasal Mask and Breathing ...</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>Patterson Dental</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
-        </is>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="G101" s="9" t="n">
-        <v>12</v>
-      </c>
+          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
       <c r="H101" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -7103,38 +7037,22 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M101" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N101" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O101" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L101" s="9" t="inlineStr"/>
+      <c r="M101" s="9" t="inlineStr"/>
+      <c r="N101" s="9" t="inlineStr"/>
+      <c r="O101" s="9" t="inlineStr"/>
       <c r="P101" s="10" t="inlineStr">
         <is>
-          <t>Product name includes '-2 Low Profile', which might indicate a different product version</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -7151,24 +7069,28 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Porter Silhouette Low Profile Nasal Mask and Breathing ...</t>
+          <t>Porter Silhouette Mask Variety</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Patterson Dental</t>
+          <t>Prime Dental Supply</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="n"/>
-      <c r="G102" s="5" t="n"/>
+          <t>https://www.primedentalsupply.com/silhouette-mask-variety-12-pack-3-of-each-size-pediatric-small-medium-large-porter-sil2-var-4x3</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>This item is ineligible for the coupon code.</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -7177,18 +7099,34 @@
         </is>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="5" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr"/>
-      <c r="N102" s="5" t="inlineStr"/>
-      <c r="O102" s="5" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P102" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>different variant (variety pack instead of medium)</t>
         </is>
       </c>
     </row>
@@ -7205,26 +7143,24 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Silhouette Nasal Mask User Manual - Dentserve</t>
+          <t>PORTER: Nitrous Oxide Accessories</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>dentserve.com</t>
+          <t>Dental Health Products, Inc.</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>https://www.dentserve.com/mwdownloads/download/link/id/9270</t>
+          <t>https://www.dhpsupply.com/products/39027/Anesthetics-Nitrous-Oxide-Accessories/&amp;mfg=PORTER&amp;pg=4</t>
         </is>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="G103" s="9" t="n">
-        <v>12</v>
-      </c>
+      <c r="G103" s="9" t="n"/>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>Order in case of 12 Circuits</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr">
@@ -7244,37 +7180,39 @@
       <c r="O103" s="9" t="inlineStr"/>
       <c r="P103" s="10" t="inlineStr">
         <is>
-          <t>price None failed sanity vs Schein unit 120.37</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>SILHOUETTE MEDIUM, 12 PK Ea</t>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>Silhouette 2 Low Profile Nasal Masks Medium 12/pack</t>
+          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Dental Health Products</t>
+          <t>Bound Tree Medical</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="n"/>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="n">
+        <v>30</v>
+      </c>
       <c r="G104" s="5" t="n"/>
       <c r="H104" s="6" t="inlineStr">
         <is>
@@ -7283,7 +7221,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="J104" s="5" t="n">
@@ -7298,7 +7236,7 @@
       <c r="O104" s="5" t="inlineStr"/>
       <c r="P104" s="6" t="inlineStr">
         <is>
-          <t>login required for pricing (public pricing only)</t>
+          <t>not scraped — enough verified candidates found</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7267,7 @@
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>14.99</v>
+        <v>51.4</v>
       </c>
       <c r="G105" s="9" t="n"/>
       <c r="H105" s="10" t="inlineStr">
@@ -7371,21 +7309,21 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Syringe Luer Lock 3cc Low Dead Space Plunger w</t>
+          <t>3mL Luer-Lock Syringe, 100-PK</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Ibis Scientific</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/exel-international-inc-syringe-luer-lock-3cc-low-dead-space-plunger-with-cap/</t>
+          <t>https://www.ibisscientific.com/3ml-luer-lock-syringe-100-pk/</t>
         </is>
       </c>
       <c r="F106" s="8" t="n">
-        <v>20.34</v>
+        <v>93.75</v>
       </c>
       <c r="G106" s="5" t="n"/>
       <c r="H106" s="6" t="inlineStr">
@@ -7427,23 +7365,25 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Exel 3cc Luer Lock Syringe with Needle | 100 Pack</t>
+          <t>maxill Luer Lock Standard Syringe, 3 cc, 100/Box - Net32</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Medical and Lab Supplies</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
+          <t>https://www.net32.com/ec/maxill-luer-lock-standard-syringe-3-cc-d-178103</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G107" s="9" t="n"/>
+        <v>10.99</v>
+      </c>
+      <c r="G107" s="9" t="n">
+        <v>100</v>
+      </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -7451,22 +7391,38 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="9" t="inlineStr"/>
-      <c r="O107" s="9" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O107" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P107" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand name, but same product type</t>
         </is>
       </c>
     </row>
@@ -7483,23 +7439,25 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
+          <t>Vista Apex Luer Lock Syringes, 3cc, 100/Box - Net32</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Medex Supply</t>
+          <t>net32.com</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
+          <t>https://www.net32.com/ec/vista-luer-lock-3cc-syringe-autoclavable-non-d-73624</t>
         </is>
       </c>
       <c r="F108" s="8" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="G108" s="5" t="n"/>
+        <v>16.7</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -7507,22 +7465,38 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="5" t="inlineStr"/>
-      <c r="M108" s="5" t="inlineStr"/>
-      <c r="N108" s="5" t="inlineStr"/>
-      <c r="O108" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand name, but same product type</t>
         </is>
       </c>
     </row>
@@ -7539,23 +7513,25 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>McKesson Safety Hypodermic Syringe 3 mL</t>
+          <t>Exel 3cc Luer Lock Syringe with Needle | 100 Pack</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>Medical and Lab Supplies</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/safety-hypodermic-syringe-with-needle-mckesson-prevent%C2%AE-3-ml-1-1-2-inch-22-gauge-hinged-safety-needle-ultra-thin-wall</t>
+          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="G109" s="9" t="n"/>
+        <v>20.95</v>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>100</v>
+      </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -7563,22 +7539,38 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="9" t="inlineStr"/>
-      <c r="O109" s="9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O109" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P109" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different variant (sterile with needle) and brand name</t>
         </is>
       </c>
     </row>
@@ -7595,23 +7587,25 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Irrigating Products - Endodontics</t>
+          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>Medex Supply</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/irrigating-products/</t>
+          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
         </is>
       </c>
       <c r="F110" s="8" t="n">
-        <v>23.74</v>
-      </c>
-      <c r="G110" s="5" t="n"/>
+        <v>15.95</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -7619,22 +7613,38 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="5" t="inlineStr"/>
-      <c r="M110" s="5" t="inlineStr"/>
-      <c r="N110" s="5" t="inlineStr"/>
-      <c r="O110" s="5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P110" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Same product type and no brand name</t>
         </is>
       </c>
     </row>
@@ -7651,22 +7661,20 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Endo Irrigation Syringes &amp; Half Cut Needles, 3 cc, 27 Ga ...</t>
+          <t>Luer Lock Syringe 3cc Bag of 100 | Benco Dental</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Frontier Dental Supply</t>
+          <t>shop.benco.com</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>https://frontierdental.com/us/en/product/endo-irrigation-syringes-half-cut-needles-3-cc-27-ga-yellow-100-pk-en27h-33071</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>27</v>
-      </c>
+          <t>https://shop.benco.com/Product/2503-444/luer-lock-syringe-3cc-bag-of-100</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n"/>
       <c r="G111" s="9" t="n"/>
       <c r="H111" s="10" t="inlineStr">
         <is>
@@ -7675,7 +7683,7 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
@@ -7690,7 +7698,7 @@
       <c r="O111" s="9" t="inlineStr"/>
       <c r="P111" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -7707,23 +7715,25 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
+          <t>3cc Luer Lock Syringes – American Dental Accessories, Inc.</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Bound Tree Medical</t>
+          <t>amerdental.com</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+          <t>https://amerdental.com/collections/exam-hygiene/products/luer-lock-syringes-3cc</t>
         </is>
       </c>
       <c r="F112" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G112" s="5" t="n"/>
+        <v>10.95</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>100</v>
+      </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -7731,22 +7741,38 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="5" t="inlineStr"/>
-      <c r="M112" s="5" t="inlineStr"/>
-      <c r="N112" s="5" t="inlineStr"/>
-      <c r="O112" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P112" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Same product type and no brand name, but marketing name variation</t>
         </is>
       </c>
     </row>
@@ -7763,21 +7789,21 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Essentials 12cc Luer Lock Syringe, 100/Pk</t>
+          <t>Luer Lock Syringes 3cc 100/Pk | Guaranteed Lowest Price | Crazy ...</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/essentials-12cc-luer-lock-syringe-100-pk-d-188871</t>
+          <t>https://www.crazydentalprices.com/Luer-Lock-Syringes-3cc-100-Pk</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>27.85</v>
+        <v>16.7</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>100</v>
@@ -7789,39 +7815,55 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="9" t="inlineStr"/>
-      <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="9" t="inlineStr"/>
-      <c r="O113" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O113" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P113" s="10" t="inlineStr">
         <is>
-          <t>volume/size mismatch after normalization</t>
+          <t>Same product type and no brand name</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Vista - Luer Lock Syringes - 3cc 100/pack, 316030</t>
+          <t>Clinpro Sealant, Refill Syringes, 1.2 ml, 1/Pk</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -7831,30 +7873,30 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>https://frontierdental.com/us/en/product/vista-luer-lock-syringes-3cc-100-pack-137173</t>
+          <t>https://www.frontierdental.com/us/en/product/clinpro-sealant-refill-syringes-1-2-ml-1-pk-37628</t>
         </is>
       </c>
       <c r="F114" s="8" t="n">
-        <v>10.96</v>
+        <v>16.66</v>
       </c>
       <c r="G114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="n">
-        <v>77</v>
-      </c>
       <c r="K114" s="5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
@@ -7863,7 +7905,7 @@
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr">
@@ -7878,42 +7920,40 @@
       </c>
       <c r="P114" s="6" t="inlineStr">
         <is>
-          <t>Different brand name (Vista) but same product type</t>
+          <t>Exact match with all criteria</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Best Selling Products – Page 7</t>
+          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>My DDS Supply</t>
+          <t>Tri County Dental Supply</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>https://myddssupply.com/collections/best-selling-products?page=7</t>
+          <t>/goto?url=CAES1wEB7keqTT_XZSZagq-B_Gi70vAKYBiHzHUzGeLvarQO-l_oih_8Wb_jgup_2EULbL-S2Sy4rsLBWxjPR68GM1fKNDODvNqASMN3AAi_pd0jAn8u5-cO1UrlTh_pm9ut_SnJMCRlqvZaLSewMHMjdMuGTfEXBwa1x8jub5NhBzTlYPuU9RdoDQtsWkvWP39bqvNK_6umEQ8id4jP1lXEqvuPh5Be5pzPFitS7K8e1EaxMtP-2_HnvdRwlVHaOLOt_ZAaJdS7rfpotk0PKny1K951s2SEPMY4eA%3D%3D</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>91.98999999999999</v>
-      </c>
-      <c r="G115" s="9" t="n">
-        <v>2000</v>
-      </c>
+        <v>25.95</v>
+      </c>
+      <c r="G115" s="9" t="n"/>
       <c r="H115" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -7925,53 +7965,67 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="9" t="inlineStr"/>
-      <c r="M115" s="9" t="inlineStr"/>
-      <c r="N115" s="9" t="inlineStr"/>
-      <c r="O115" s="9" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O115" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P115" s="10" t="inlineStr">
         <is>
-          <t>price 91.99 failed sanity vs Schein unit 17.61</t>
+          <t>Insufficient information and mismatched product name</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>RMH3 Dental Luer-Lock Endo Irrigation Syringes, 3cc, 100/ ...</t>
+          <t>3M Clinpro Sealant Refill, Syringe</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>The Dentists Supply Company</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/rmh3-luerlock-endo-irrigation-syringes-3cc-100-d-168420</t>
+          <t>/goto?url=CAESmgIB7keqTR9E0UmHOt1TFxBbMH5lKYfxmeEwkoHR0NiWwOTZLbus0e2hpMOnwIr8uofDaqsjjfAw7plUCTYjc5bn1Vpj1zxd8OvP4dJZeLF7RXKlgrW_x6pP4YTuEM2mExLWTQWolxcw3eLulfPQ7eOFINwyFEP9xkv7dtSjTQiF9Dp9Vs8ewf7yPXrsDlmdN_JFhMsxanrn2cKQVgVrwJ2PZG99oHKg4OE_xMQqpyws_72n8cf6B5Ri8AspxOOr8zvFcd-9Gy1ZqNyMAqhGklR0j4Bn4DCaMwukYfaJdt0h6sa9n51wHbtW42iRF1RFbb9-76S7TgfpwkBrxGRJ5XcRrBMZnq5TxzIvOeg8IY-xGNbUDG5T-mi6wJI%3D</t>
         </is>
       </c>
       <c r="F116" s="8" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>100</v>
-      </c>
+        <v>30.12</v>
+      </c>
+      <c r="G116" s="5" t="n"/>
       <c r="H116" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -7979,14 +8033,14 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J116" s="5" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
@@ -8000,52 +8054,50 @@
       </c>
       <c r="N116" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O116" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P116" s="6" t="inlineStr">
         <is>
-          <t>Different product name (RMH3 Dental Luer-Lock Endo Irrigation Syringes) but same product family and specs</t>
+          <t>Insufficient information and mismatched product name</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>5701400</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx</t>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>3D Dental Luer Lock Syringe 6cc 100/Bx</t>
+          <t>iris® Pit and Fissure Sealant A2 1.2ml Syringe Pack of 4</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>SurgiMac Dental Supply</t>
+          <t>Benco Dental</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>https://surgimac.com/products/luer-lock-syringe-6cc-100-bx</t>
+          <t>https://shop.benco.com/Product/4006-862/iris-pit-and-fissure-sealant-a2-12ml-syringe-pack-</t>
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="G117" s="9" t="n">
-        <v>100</v>
-      </c>
+        <v>77.98999999999999</v>
+      </c>
+      <c r="G117" s="9" t="n"/>
       <c r="H117" s="10" t="inlineStr">
         <is>
           <t>—</t>
@@ -8068,7 +8120,7 @@
       <c r="O117" s="9" t="inlineStr"/>
       <c r="P117" s="10" t="inlineStr">
         <is>
-          <t>volume/size mismatch after normalization</t>
+          <t>login required for pricing (public pricing only)</t>
         </is>
       </c>
     </row>
@@ -8085,31 +8137,31 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>3M™ Clinpro™ Sealant</t>
+          <t>Dental Pit and Fissure Sealants</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Top Quality Manufacturing, LLC</t>
+          <t>Dentalcompare.com</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n">
-        <v>33.25</v>
-      </c>
-      <c r="G118" s="5" t="n"/>
+          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H118" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Not Available</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J118" s="5" t="n">
@@ -8124,104 +8176,124 @@
       <c r="O118" s="5" t="inlineStr"/>
       <c r="P118" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>price None failed sanity vs Schein unit 32.2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Sealant (Solventum) | Dental Product</t>
+          <t>Evacuation System Cleaners - Sky Dental Supply</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Pearson Dental Supply</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13311&amp;catid=10955&amp;subcatid=16163&amp;pid=37884</t>
+          <t>https://www.skydentalsupply.com/evac-cleaner/</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="G119" s="9" t="n"/>
+        <v>39.99</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BUY 3 GET 1 FREE</t>
         </is>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="9" t="inlineStr"/>
-      <c r="M119" s="9" t="inlineStr"/>
-      <c r="N119" s="9" t="inlineStr"/>
-      <c r="O119" s="9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M119" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O119" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P119" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different brand and product name</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Refill 1.2ml Syringe</t>
+          <t>Purevac SC Evacuation Cleaner 2L/Bt | Guaranteed Lowest Price</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Crazy Dental Price Club</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
+          <t>https://www.crazydentalprices.com/Purevac-SC-21132</t>
         </is>
       </c>
       <c r="F120" s="8" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="G120" s="5" t="n"/>
+        <v>70.48999999999999</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="H120" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4 Get 1 Free! (Limit 5)</t>
         </is>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J120" s="5" t="n">
@@ -8236,48 +8308,50 @@
       <c r="O120" s="5" t="inlineStr"/>
       <c r="P120" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>volume/size mismatch after normalization</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant - Syringe Tips Refill, Black 10/Pk</t>
+          <t>Purevac SC Evacuation System Cleaner</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Net32</t>
+          <t>Scott's Dental Supply</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/clinpro-sealant-syringe-tips-refill-black-10-d-49828</t>
+          <t>https://www.scottsdental.com/purevac-sc.html</t>
         </is>
       </c>
       <c r="F121" s="12" t="n">
-        <v>41.94</v>
-      </c>
-      <c r="G121" s="9" t="n"/>
+        <v>76.95</v>
+      </c>
+      <c r="G121" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4 Get 1 FREE; Limit 5 per Practice</t>
         </is>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
@@ -8292,209 +8366,259 @@
       <c r="O121" s="9" t="inlineStr"/>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>volume/size mismatch after normalization</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Mixing Well With Cover 4Bx</t>
+          <t>Purevac SC Evacuation Cleaner 5L/Bt | Guaranteed Lowest Price</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>crazydentalprices.com</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/3m-clinpro-sealant-mixing-well-with-cover-12621mw-4-per-box/</t>
+          <t>https://www.crazydentalprices.com/Purevac-SC-21135</t>
         </is>
       </c>
       <c r="F122" s="8" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="G122" s="5" t="n"/>
+        <v>154.49</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pack quantity is 5, which is larger than the reference product</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="J122" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="5" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr"/>
-      <c r="N122" s="5" t="inlineStr"/>
-      <c r="O122" s="5" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O122" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Different pack quantity</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Solventum | Create beautiful, healthy smiles while growing your ...</t>
+          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>DDS Dental Supplies</t>
+          <t>US Dental Depot</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/solventum/?page=71</t>
+          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
         </is>
       </c>
       <c r="F123" s="12" t="n">
-        <v>43.42</v>
-      </c>
-      <c r="G123" s="9" t="n"/>
+        <v>194.45</v>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="9" t="inlineStr"/>
-      <c r="M123" s="9" t="inlineStr"/>
-      <c r="N123" s="9" t="inlineStr"/>
-      <c r="O123" s="9" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M123" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N123" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O123" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>not scraped — enough verified candidates found</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Dentsply Sirona - Purevac SC Evacuation System Cleaner 5L</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Curio.Dental</t>
+          <t>Dental City</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>https://curio.dental/collections/all-products</t>
+          <t>https://www.dentalcity.com/product/11656/dentsply-sirona-purevac-sc-evacuation-system-cleaner-5l</t>
         </is>
       </c>
       <c r="F124" s="8" t="n">
-        <v>4.81</v>
+        <v>197.73</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H124" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Buy 4, Get 1 Free</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="J124" s="5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="5" t="inlineStr"/>
-      <c r="M124" s="5" t="inlineStr"/>
-      <c r="N124" s="5" t="inlineStr"/>
-      <c r="O124" s="5" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
-          <t>volume/size mismatch after normalization</t>
+          <t>Exact match</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>7770371</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>3M Clinpro Sealant Refill Bottle, 12622, 6 mL ...</t>
+          <t>Purevac® SC Evacuation System Cleaner - 2 Liter</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Supply Clinic</t>
+          <t>Patterson Dental</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-refill-bottle-12622-6-ml-bottle-1-bottle-pack-3m-12622</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>17.54</v>
-      </c>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="n"/>
       <c r="G125" s="9" t="n"/>
       <c r="H125" s="10" t="inlineStr">
         <is>
@@ -8517,762 +8641,6 @@
       <c r="N125" s="9" t="inlineStr"/>
       <c r="O125" s="9" t="inlineStr"/>
       <c r="P125" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant, Refill Syringes, 1.2 ml, 1/Pk</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>Frontier Dental Supply</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>https://www.frontierdental.com/us/en/product/clinpro-sealant-refill-syringes-1-2-ml-1-pk-37628</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="J126" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L126" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M126" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N126" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O126" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P126" s="6" t="inlineStr">
-        <is>
-          <t>Exact match with all criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light ...</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>Tri County Dental Supply</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="G127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="J127" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K127" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L127" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M127" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N127" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O127" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P127" s="10" t="inlineStr">
-        <is>
-          <t>Different variant (with 10 tips) and name mismatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>3M Clinpro Sealant Refill, Syringe</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>The Dentists Supply Company</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Treatments-%26-Prescription-Materials/Sealants/3M-Clinpro-Sealant-Refill%2C-Syringe/p/310009-101</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>1/kit</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="J128" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M128" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N128" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O128" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P128" s="6" t="inlineStr">
-        <is>
-          <t>Exact match with all criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant</t>
-        </is>
-      </c>
-      <c r="D129" s="9" t="inlineStr">
-        <is>
-          <t>Amtouch</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>36.29</v>
-      </c>
-      <c r="G129" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H129" s="10" t="inlineStr">
-        <is>
-          <t>Larger pack (2)</t>
-        </is>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J129" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="K129" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M129" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N129" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O129" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P129" s="10" t="inlineStr">
-        <is>
-          <t>Different size/form (bottles) and pack quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>Dental Pit and Fissure Sealants</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>Dentalcompare.com</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="n"/>
-      <c r="G130" s="5" t="n"/>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="5" t="inlineStr"/>
-      <c r="M130" s="5" t="inlineStr"/>
-      <c r="N130" s="5" t="inlineStr"/>
-      <c r="O130" s="5" t="inlineStr"/>
-      <c r="P130" s="6" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea</t>
-        </is>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>Clinpro Sealant - 1.2 ml Syringe Refill with 10 ...</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>Net32</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/clinpro-sealant-12-ml-syringe-refill-10-d-49827</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="G131" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H131" s="10" t="inlineStr">
-        <is>
-          <t>Larger pack (10 syringe tips)</t>
-        </is>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="J131" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="K131" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="L131" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M131" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N131" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O131" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P131" s="10" t="inlineStr">
-        <is>
-          <t>Different pack quantity and includes 10 syringe tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>Evacuation System Cleaners - Sky Dental Supply</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>skydentalsupply.com</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>https://www.skydentalsupply.com/evac-cleaner/</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="n">
-        <v>39.99</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>BUY 3 GET 1 FREE</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N132" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O132" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P132" s="6" t="inlineStr">
-        <is>
-          <t>Different brand and product name, also variant 'Sable' does not match</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation System Cleaner</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr">
-        <is>
-          <t>Scott's Dental Supply</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scottsdental.com/purevac-sc.html</t>
-        </is>
-      </c>
-      <c r="F133" s="12" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="G133" s="9" t="n"/>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="9" t="inlineStr"/>
-      <c r="M133" s="9" t="inlineStr"/>
-      <c r="N133" s="9" t="inlineStr"/>
-      <c r="O133" s="9" t="inlineStr"/>
-      <c r="P133" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>DENTSPLY - Purevac SC Evacuation System Cleaner</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>US Dental Depot</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>https://usdentaldepot.com/purevac-sc-evacuation-system-cleane-dentsply-21135</t>
-        </is>
-      </c>
-      <c r="F134" s="8" t="n">
-        <v>194.45</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M134" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N134" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O134" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P134" s="6" t="inlineStr">
-        <is>
-          <t>Exact match in brand, product name, size and pack quantity</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>Dentsply Sirona - Purevac SC Evacuation System Cleaner 5L</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>Dental City</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>https://www.dentalcity.com/product/11656/dentsply-sirona-purevac-sc-evacuation-system-cleaner-5l</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="n">
-        <v>197.73</v>
-      </c>
-      <c r="G135" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H135" s="10" t="inlineStr">
-        <is>
-          <t>Pack quantity is 5, which is a case</t>
-        </is>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="J135" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="K135" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="L135" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M135" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N135" s="9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O135" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P135" s="10" t="inlineStr">
-        <is>
-          <t>Different pack quantity, but same product family and size</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Purevac SC Evacuation Cleaner 5 Liter Ea</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>Purevac® SC Evacuation System Cleaner - 2 Liter</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Patterson Dental</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="n"/>
-      <c r="G136" s="5" t="n"/>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>rejected</t>
-        </is>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="5" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr"/>
-      <c r="N136" s="5" t="inlineStr"/>
-      <c r="O136" s="5" t="inlineStr"/>
-      <c r="P136" s="6" t="inlineStr">
         <is>
           <t>login required for pricing (public pricing only)</t>
         </is>
@@ -9406,17 +8774,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9526,7 +8883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9575,7 +8932,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/120-320062/DHP-Topical-Anesthetic-Gel/</t>
+          <t>https://www.darbydental.com/9502997-01.html</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -9587,12 +8944,12 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>5700360</t>
+          <t>7772551</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>https://intl.usdentaldepot.com/gel-1-oz-btl-strawberry-pro-line-018-024</t>
+          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -9604,12 +8961,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>2906663</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6094-559/mixing-tips-42-mm-yellow-bag-of-50?Source=Similar.Proton</t>
+          <t>https://shop.benco.com/Product/2420-006/luxatemp-automix-plus-shade-a2-refill-kit</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -9621,12 +8978,12 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>5703375</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6589-659/oral-b-glide-healthy-gums-floss-160m-refill-unflav</t>
+          <t>https://shop.benco.com/Product/1707-860/assorted-colors-denture-box-pack-of-12</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -9638,12 +8995,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>3250497</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>https://www.dcdental.com/Oral-B-Glide-Healthy-Gums-Floss-160m-Disp-Vial-1-Bx-Unflavored</t>
+          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -9655,12 +9012,12 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>1459489</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>https://topqualitygloves.com/products/clinpro%E2%84%A2-in-office-2-1-naf-clear-fluoride-treatment</t>
+          <t>https://www.dhpsupply.com/products/39027/Anesthetics-Nitrous-Oxide-Accessories/&amp;mfg=PORTER&amp;pg=4</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -9672,12 +9029,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>7772551</t>
+          <t>5701400</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>https://shop.benco.com/Product/6300-263/3m-clinpro-clear-fluoride-treatment-mint-flavor-05</t>
+          <t>https://shop.benco.com/Product/2503-444/luer-lock-syringe-3cc-bag-of-100</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -9689,12 +9046,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>7770371</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/small-equipment/nitrous-oxide-products/porter-silhouette-low-profile-nasal-mask-and-breathing-circuit/PIF_744184</t>
+          <t>https://shop.benco.com/Product/4006-862/iris-pit-and-fissure-sealant-a2-12ml-syringe-pack-</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -9706,83 +9063,15 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1459489</t>
+          <t>3120099</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>https://www.dhpsupply.com/item/130-SIL2MED12/Silhouette-2-Low-Profile-Nasal/</t>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-refill-bottle-12622-6-ml-bottle-1-bottle-pack-3m-12622</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>7770371</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.dentalcompare.com/Restorative-Dentistry/4407-Pit-and-Fissure-Sealants/Compare/?compare=33042%2C2802134%2C35292%2C33038%2C33035&amp;catid=4407</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scottsdental.com/purevac-sc.html</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>login required for pricing (public pricing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>3120099</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/076659049</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>login required for pricing (public pricing only)</t>
         </is>
@@ -9803,10 +9092,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9836,7 +9121,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parsed Order Audit  ·  tmpdaqus_dx.pdf</t>
+          <t>Parsed Order Audit  ·  tmplcf3mmir.pdf</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
